--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFD380E-5CA9-4839-9B42-542F58B99725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEF3C76-B35F-42F2-8591-A1E157E1C091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="270">
   <si>
     <t>Price</t>
   </si>
@@ -790,7 +790,67 @@
     <t>Partial trim to lock profits, its breaking out today, need confirmation tomorrow, stop trailed.</t>
   </si>
   <si>
-    <t>nvda</t>
+    <t>Overnight gap invalidated thesis, still not in the right trend</t>
+  </si>
+  <si>
+    <t>Still is not showing strengthe and big volatility</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>Stopped out. I tighten before travel and noise took me out</t>
+  </si>
+  <si>
+    <t>Apparently another false break out, big pull back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong pull back in the market. Stopped out after tightening for caution </t>
+  </si>
+  <si>
+    <t>PLNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stopped out for AI collapse </t>
+  </si>
+  <si>
+    <t>GAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop hunt </t>
+  </si>
+  <si>
+    <t>Bad setup, it never went on the direction expected</t>
+  </si>
+  <si>
+    <t>Bad entry, the stock got rejected in 28</t>
+  </si>
+  <si>
+    <t>40 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stopped out. It loss momentum and started fading </t>
+  </si>
+  <si>
+    <t>APLD</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Liquidity in 55 levels. Bad entry</t>
+  </si>
+  <si>
+    <t>LULU</t>
+  </si>
+  <si>
+    <t>bad entry for trying to anticipate the moving of the stock before showing clear signs</t>
+  </si>
+  <si>
+    <t>st</t>
+  </si>
+  <si>
+    <t>Rally started, take a look of the momentum, and the volume, it can become a good trade</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -1239,7 +1299,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1294,7 +1354,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>191.76</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1319,7 +1379,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>184.095</v>
+        <v>34.569999999999993</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1387,7 +1447,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>7.664999999999992</v>
+        <v>1.5900000000000034</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1412,7 +1472,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>6.1317677756033984</v>
+        <v>29.559748427672893</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1437,7 +1497,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>21.380892782644974</v>
+        <v>113.38495575221241</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1462,7 +1522,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>6.1317677756033984</v>
+        <v>29.559748427672893</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1583,14 +1643,14 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>39.74</v>
+        <v>40.97</v>
       </c>
       <c r="C18">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>38.78</v>
+        <v>40.024999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1598,14 +1658,14 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>77.92</v>
+        <v>79.58</v>
       </c>
       <c r="C19">
         <v>1.68</v>
       </c>
       <c r="D19">
-        <f t="shared" si="0"/>
-        <v>75.400000000000006</v>
+        <f>B19-(0.5*C19)</f>
+        <v>78.739999999999995</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1898,14 +1958,14 @@
         <v>67</v>
       </c>
       <c r="B39">
-        <v>57.51</v>
+        <v>58.4</v>
       </c>
       <c r="C39">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="D39">
-        <f>B39-(1*C39)</f>
-        <v>56.07</v>
+        <f>B39-(1.5*C39)</f>
+        <v>55.85</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2078,14 +2138,14 @@
         <v>19</v>
       </c>
       <c r="B51">
-        <v>38.479999999999997</v>
+        <v>40.950000000000003</v>
       </c>
       <c r="C51">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="D51">
         <f>B51-(1.5*C51)</f>
-        <v>37.669999999999995</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2243,14 +2303,14 @@
         <v>122</v>
       </c>
       <c r="B62">
-        <v>8.52</v>
+        <v>10.08</v>
       </c>
       <c r="C62">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="D62">
         <f>B62-(1*C62)</f>
-        <v>7.4899999999999993</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2273,14 +2333,14 @@
         <v>124</v>
       </c>
       <c r="B64">
-        <v>154.36000000000001</v>
+        <v>151.6</v>
       </c>
       <c r="C64">
         <v>2.94</v>
       </c>
       <c r="D64">
         <f>B64-(1*C64)</f>
-        <v>151.42000000000002</v>
+        <v>148.66</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2288,14 +2348,14 @@
         <v>125</v>
       </c>
       <c r="B65">
-        <v>55.65</v>
+        <v>58.96</v>
       </c>
       <c r="C65">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="D65">
         <f>B65-(1.5*C65)</f>
-        <v>53.04</v>
+        <v>55.72</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2498,14 +2558,14 @@
         <v>143</v>
       </c>
       <c r="B79">
-        <v>6.07</v>
+        <v>5.32</v>
       </c>
       <c r="C79">
         <v>0.41</v>
       </c>
       <c r="D79">
         <f>B79-(1.5*C79)</f>
-        <v>5.4550000000000001</v>
+        <v>4.7050000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2528,14 +2588,14 @@
         <v>145</v>
       </c>
       <c r="B81">
-        <v>32.51</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="C81">
-        <v>1.1299999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="D81">
         <f>B81-(1.5*C81)</f>
-        <v>30.814999999999998</v>
+        <v>34.569999999999993</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2888,14 +2948,14 @@
         <v>246</v>
       </c>
       <c r="B105">
-        <v>7.96</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="C105">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="D105">
         <f>B105-(1*C105)</f>
-        <v>7.6899999999999995</v>
+        <v>7.9399999999999995</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -2926,6 +2986,96 @@
       <c r="D107">
         <f>B107-(1.5*C107)</f>
         <v>52.54</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>251</v>
+      </c>
+      <c r="B108">
+        <v>19.234999999999999</v>
+      </c>
+      <c r="C108">
+        <v>0.4</v>
+      </c>
+      <c r="D108">
+        <f>B108-(1*C108)</f>
+        <v>18.835000000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>255</v>
+      </c>
+      <c r="B109">
+        <v>92.18</v>
+      </c>
+      <c r="C109">
+        <v>2.82</v>
+      </c>
+      <c r="D109">
+        <f>B109-(1.5*C109)</f>
+        <v>87.95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>257</v>
+      </c>
+      <c r="B110">
+        <v>28.97</v>
+      </c>
+      <c r="C110">
+        <v>0.9</v>
+      </c>
+      <c r="D110">
+        <f>B110-(1.5*C110)</f>
+        <v>27.619999999999997</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>263</v>
+      </c>
+      <c r="B111">
+        <v>38.32</v>
+      </c>
+      <c r="C111">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="D111">
+        <f>B111-(1.5*C111)</f>
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>264</v>
+      </c>
+      <c r="B112">
+        <v>33.93</v>
+      </c>
+      <c r="C112">
+        <v>2.08</v>
+      </c>
+      <c r="D112">
+        <f>B112-(1.5*C112)</f>
+        <v>30.81</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>266</v>
+      </c>
+      <c r="B113">
+        <v>181.5</v>
+      </c>
+      <c r="C113">
+        <v>7.21</v>
+      </c>
+      <c r="D113">
+        <f>B113-(1.5*C113)</f>
+        <v>170.685</v>
       </c>
     </row>
   </sheetData>
@@ -3160,7 +3310,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2A77BB-0F93-4C87-9B0A-B8954405005E}">
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -3176,7 +3326,7 @@
       </c>
       <c r="B1" s="3">
         <f>COUNTIF(M:M,"Win")/COUNTA(M:M)</f>
-        <v>0.5056179775280899</v>
+        <v>0.48039215686274511</v>
       </c>
       <c r="C1" t="s">
         <v>92</v>
@@ -3188,7 +3338,7 @@
       </c>
       <c r="B2">
         <f>AVERAGEIF(M:M,"Win",I:I)</f>
-        <v>10.059257090741108</v>
+        <v>9.7235064318751352</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -3197,7 +3347,7 @@
       </c>
       <c r="B3">
         <f>AVERAGEIF(M:M,"Loss",I:I)</f>
-        <v>-4.5206462908951899</v>
+        <v>-4.3531092320495279</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -3206,7 +3356,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.45452216601960527</v>
+        <v>0.36974810813780523</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -3215,7 +3365,7 @@
       </c>
       <c r="B5">
         <f>(B1*B2+(1-B1)*B3)</f>
-        <v>2.8512149694827138</v>
+        <v>2.4091865280711442</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -4100,14 +4250,14 @@
       </c>
       <c r="D27">
         <f>VLOOKUP(B27,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="E27">
         <v>52.95</v>
       </c>
       <c r="F27">
         <f t="shared" si="5"/>
-        <v>43.72</v>
+        <v>43.089999999999996</v>
       </c>
       <c r="G27" t="s">
         <v>117</v>
@@ -4118,7 +4268,7 @@
       </c>
       <c r="J27">
         <f t="shared" si="26"/>
-        <v>5.6334988128642332</v>
+        <v>6.9933088711418137</v>
       </c>
       <c r="K27">
         <f t="shared" si="27"/>
@@ -4126,7 +4276,7 @@
       </c>
       <c r="L27">
         <f t="shared" si="28"/>
-        <v>2.5363984674329529</v>
+        <v>2.0432098765432101</v>
       </c>
       <c r="M27" t="str">
         <f t="shared" si="29"/>
@@ -4148,14 +4298,14 @@
       </c>
       <c r="D28">
         <f>VLOOKUP(B28,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="E28">
         <v>53.84</v>
       </c>
       <c r="F28">
         <f t="shared" si="5"/>
-        <v>43.72</v>
+        <v>43.089999999999996</v>
       </c>
       <c r="G28" t="s">
         <v>117</v>
@@ -4166,7 +4316,7 @@
       </c>
       <c r="J28">
         <f t="shared" si="26"/>
-        <v>5.6334988128642332</v>
+        <v>6.9933088711418137</v>
       </c>
       <c r="K28">
         <f t="shared" si="27"/>
@@ -4174,7 +4324,7 @@
       </c>
       <c r="L28">
         <f t="shared" si="28"/>
-        <v>2.8773946360153291</v>
+        <v>2.3179012345679015</v>
       </c>
       <c r="M28" t="str">
         <f t="shared" si="29"/>
@@ -4292,14 +4442,14 @@
       </c>
       <c r="D31">
         <f>VLOOKUP(B31,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="E31">
         <v>7.47</v>
       </c>
       <c r="F31">
         <f t="shared" si="5"/>
-        <v>6.9749999999999996</v>
+        <v>6.6</v>
       </c>
       <c r="G31" t="s">
         <v>105</v>
@@ -4310,7 +4460,7 @@
       </c>
       <c r="J31">
         <f t="shared" si="26"/>
-        <v>18.133802816901408</v>
+        <v>22.535211267605636</v>
       </c>
       <c r="K31">
         <f t="shared" si="27"/>
@@ -4318,7 +4468,7 @@
       </c>
       <c r="L31">
         <f t="shared" si="28"/>
-        <v>-0.67961165048543681</v>
+        <v>-0.54687499999999989</v>
       </c>
       <c r="M31" t="str">
         <f t="shared" si="29"/>
@@ -4340,14 +4490,14 @@
       </c>
       <c r="D32">
         <f>VLOOKUP(B32,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="E32">
         <v>54.09</v>
       </c>
       <c r="F32">
         <f t="shared" si="5"/>
-        <v>43.72</v>
+        <v>43.089999999999996</v>
       </c>
       <c r="G32" t="s">
         <v>155</v>
@@ -4358,7 +4508,7 @@
       </c>
       <c r="J32">
         <f t="shared" si="26"/>
-        <v>5.6334988128642332</v>
+        <v>6.9933088711418137</v>
       </c>
       <c r="K32">
         <f t="shared" si="27"/>
@@ -4366,7 +4516,7 @@
       </c>
       <c r="L32">
         <f t="shared" si="28"/>
-        <v>2.9731800766283558</v>
+        <v>2.3950617283950622</v>
       </c>
       <c r="M32" t="str">
         <f t="shared" si="29"/>
@@ -4388,14 +4538,14 @@
       </c>
       <c r="D33">
         <f>VLOOKUP(B33,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="E33">
         <v>38.75</v>
       </c>
       <c r="F33">
         <f t="shared" si="5"/>
-        <v>38.519999999999996</v>
+        <v>38.534999999999997</v>
       </c>
       <c r="G33" t="s">
         <v>155</v>
@@ -4406,7 +4556,7 @@
       </c>
       <c r="J33">
         <f t="shared" si="26"/>
-        <v>2.4316109422492427</v>
+        <v>2.3936170212765968</v>
       </c>
       <c r="K33">
         <f t="shared" si="27"/>
@@ -4414,7 +4564,7 @@
       </c>
       <c r="L33">
         <f t="shared" si="28"/>
-        <v>-0.76041666666666263</v>
+        <v>-0.77248677248676889</v>
       </c>
       <c r="M33" t="str">
         <f t="shared" si="29"/>
@@ -5345,14 +5495,14 @@
       </c>
       <c r="D53">
         <f>VLOOKUP(B53,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.1299999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="E53">
         <v>33.57</v>
       </c>
       <c r="F53">
         <f t="shared" si="5"/>
-        <v>30.825000000000003</v>
+        <v>30.930000000000003</v>
       </c>
       <c r="G53" t="s">
         <v>162</v>
@@ -5363,7 +5513,7 @@
       </c>
       <c r="J53">
         <f t="shared" si="26"/>
-        <v>5.2121771217712176</v>
+        <v>4.8892988929889292</v>
       </c>
       <c r="K53">
         <f t="shared" si="27"/>
@@ -5371,7 +5521,7 @@
       </c>
       <c r="L53">
         <f t="shared" si="28"/>
-        <v>0.61946902654867086</v>
+        <v>0.66037735849056434</v>
       </c>
       <c r="M53" t="str">
         <f t="shared" si="29"/>
@@ -6113,14 +6263,14 @@
       </c>
       <c r="D69">
         <f>VLOOKUP(B69,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="E69">
         <v>52.98</v>
       </c>
       <c r="F69">
         <f t="shared" si="5"/>
-        <v>52.95</v>
+        <v>52.32</v>
       </c>
       <c r="G69" t="s">
         <v>113</v>
@@ -6131,7 +6281,7 @@
       </c>
       <c r="J69">
         <f t="shared" si="31"/>
-        <v>4.6976241900647935</v>
+        <v>5.831533477321817</v>
       </c>
       <c r="K69">
         <f t="shared" si="32"/>
@@ -6139,7 +6289,7 @@
       </c>
       <c r="L69">
         <f t="shared" si="33"/>
-        <v>-0.98850574712643902</v>
+        <v>-0.7962962962962975</v>
       </c>
       <c r="M69" t="str">
         <f t="shared" si="34"/>
@@ -6449,14 +6599,14 @@
       </c>
       <c r="D76">
         <f>VLOOKUP(B76,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="E76">
         <v>39.049999999999997</v>
       </c>
       <c r="F76">
         <f t="shared" si="5"/>
-        <v>37.130000000000003</v>
+        <v>37.145000000000003</v>
       </c>
       <c r="G76" t="s">
         <v>183</v>
@@ -6467,7 +6617,7 @@
       </c>
       <c r="J76">
         <f t="shared" si="36"/>
-        <v>2.5203465476503037</v>
+        <v>2.4809661328432662</v>
       </c>
       <c r="K76">
         <f t="shared" si="37"/>
@@ -6475,7 +6625,7 @@
       </c>
       <c r="L76">
         <f t="shared" si="38"/>
-        <v>0.99999999999999256</v>
+        <v>1.0158730158730089</v>
       </c>
       <c r="M76" t="str">
         <f t="shared" si="39"/>
@@ -7079,7 +7229,7 @@
         <v>327.12</v>
       </c>
       <c r="F89">
-        <f t="shared" ref="F89:F97" si="40">C89-(1.5*D89)</f>
+        <f t="shared" ref="F89:F110" si="40">C89-(1.5*D89)</f>
         <v>314.98500000000001</v>
       </c>
       <c r="G89" t="s">
@@ -7278,23 +7428,23 @@
         <v>118</v>
       </c>
       <c r="I93">
-        <f t="shared" ref="I93:I97" si="41">(E93-C93)/C93*(100)</f>
+        <f t="shared" ref="I93:I110" si="41">(E93-C93)/C93*(100)</f>
         <v>-0.69353228602953898</v>
       </c>
       <c r="J93">
-        <f t="shared" ref="J93:J97" si="42">(C93-F93)/C93*100</f>
+        <f t="shared" ref="J93:J110" si="42">(C93-F93)/C93*100</f>
         <v>4.0272158881941849</v>
       </c>
       <c r="K93">
-        <f t="shared" ref="K93:K97" si="43">(E93-C93)/C93*100</f>
+        <f t="shared" ref="K93:K110" si="43">(E93-C93)/C93*100</f>
         <v>-0.69353228602953898</v>
       </c>
       <c r="L93">
-        <f t="shared" ref="L93:L97" si="44">K93/J93</f>
+        <f t="shared" ref="L93:L110" si="44">K93/J93</f>
         <v>-0.17221135029354506</v>
       </c>
       <c r="M93" t="str">
-        <f t="shared" ref="M93:M97" si="45">IF(I93&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M93:M110" si="45">IF(I93&gt;0,"Win","Loss")</f>
         <v>Loss</v>
       </c>
       <c r="N93" t="s">
@@ -7457,14 +7607,14 @@
       </c>
       <c r="D97">
         <f>VLOOKUP(B97,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="E97">
         <v>8.73</v>
       </c>
       <c r="F97">
         <f t="shared" si="40"/>
-        <v>7.5649999999999995</v>
+        <v>7.46</v>
       </c>
       <c r="G97" t="s">
         <v>113</v>
@@ -7475,7 +7625,7 @@
       </c>
       <c r="J97">
         <f t="shared" si="42"/>
-        <v>5.081555834378924</v>
+        <v>6.3989962358845647</v>
       </c>
       <c r="K97">
         <f t="shared" si="43"/>
@@ -7483,7 +7633,7 @@
       </c>
       <c r="L97">
         <f t="shared" si="44"/>
-        <v>1.8765432098765438</v>
+        <v>1.4901960784313744</v>
       </c>
       <c r="M97" t="str">
         <f t="shared" si="45"/>
@@ -7493,9 +7643,633 @@
         <v>248</v>
       </c>
     </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B98" t="s">
+        <v>68</v>
+      </c>
+      <c r="C98">
+        <v>191.76</v>
+      </c>
+      <c r="D98">
+        <f>VLOOKUP(B98,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="E98">
+        <v>184.07</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="40"/>
+        <v>184.095</v>
+      </c>
+      <c r="G98" t="s">
+        <v>176</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="41"/>
+        <v>-4.010221109720483</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="42"/>
+        <v>3.9971839799749649</v>
+      </c>
+      <c r="K98">
+        <f t="shared" si="43"/>
+        <v>-4.010221109720483</v>
+      </c>
+      <c r="L98">
+        <f t="shared" si="44"/>
+        <v>-1.0032615786040451</v>
+      </c>
+      <c r="M98" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N98" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B99" t="s">
+        <v>232</v>
+      </c>
+      <c r="C99">
+        <v>333.81</v>
+      </c>
+      <c r="D99">
+        <f>VLOOKUP(B99,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>12.93</v>
+      </c>
+      <c r="E99">
+        <v>327.33</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="40"/>
+        <v>314.41500000000002</v>
+      </c>
+      <c r="G99" t="s">
+        <v>113</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="41"/>
+        <v>-1.9412240496090645</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="42"/>
+        <v>5.8101914262604426</v>
+      </c>
+      <c r="K99">
+        <f t="shared" si="43"/>
+        <v>-1.9412240496090645</v>
+      </c>
+      <c r="L99">
+        <f t="shared" si="44"/>
+        <v>-0.33410672853828427</v>
+      </c>
+      <c r="M99" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N99" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B100" t="s">
+        <v>143</v>
+      </c>
+      <c r="C100">
+        <v>5.32</v>
+      </c>
+      <c r="D100">
+        <f>VLOOKUP(B100,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.41</v>
+      </c>
+      <c r="E100">
+        <v>5.57</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="40"/>
+        <v>4.7050000000000001</v>
+      </c>
+      <c r="G100" t="s">
+        <v>188</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="41"/>
+        <v>4.6992481203007515</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="42"/>
+        <v>11.560150375939852</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="43"/>
+        <v>4.6992481203007515</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="44"/>
+        <v>0.40650406504065029</v>
+      </c>
+      <c r="M100" t="str">
+        <f t="shared" si="45"/>
+        <v>Win</v>
+      </c>
+      <c r="N100" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B101" t="s">
+        <v>125</v>
+      </c>
+      <c r="C101">
+        <v>56.06</v>
+      </c>
+      <c r="D101">
+        <f>VLOOKUP(B101,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>2.16</v>
+      </c>
+      <c r="E101">
+        <v>54.99</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="40"/>
+        <v>52.82</v>
+      </c>
+      <c r="G101" t="s">
+        <v>176</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="41"/>
+        <v>-1.9086692829111671</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="42"/>
+        <v>5.7795219407777418</v>
+      </c>
+      <c r="K101">
+        <f t="shared" si="43"/>
+        <v>-1.9086692829111671</v>
+      </c>
+      <c r="L101">
+        <f t="shared" si="44"/>
+        <v>-0.33024691358024677</v>
+      </c>
+      <c r="M101" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N101" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B102" t="s">
+        <v>246</v>
+      </c>
+      <c r="C102">
+        <v>7.97</v>
+      </c>
+      <c r="D102">
+        <f>VLOOKUP(B102,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.34</v>
+      </c>
+      <c r="E102">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="F102">
+        <f t="shared" si="40"/>
+        <v>7.46</v>
+      </c>
+      <c r="G102" t="s">
+        <v>107</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="41"/>
+        <v>3.1367628607277402</v>
+      </c>
+      <c r="J102">
+        <f t="shared" si="42"/>
+        <v>6.3989962358845647</v>
+      </c>
+      <c r="K102">
+        <f t="shared" si="43"/>
+        <v>3.1367628607277402</v>
+      </c>
+      <c r="L102">
+        <f t="shared" si="44"/>
+        <v>0.49019607843137447</v>
+      </c>
+      <c r="M102" t="str">
+        <f t="shared" si="45"/>
+        <v>Win</v>
+      </c>
+      <c r="N102" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B103" t="s">
+        <v>207</v>
+      </c>
+      <c r="C103">
+        <v>326.01</v>
+      </c>
+      <c r="D103">
+        <f>VLOOKUP(B103,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>7.54</v>
+      </c>
+      <c r="E103">
+        <v>311.27999999999997</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="40"/>
+        <v>314.7</v>
+      </c>
+      <c r="G103" t="s">
+        <v>105</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="41"/>
+        <v>-4.5182663108493664</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="42"/>
+        <v>3.4692187356216078</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="43"/>
+        <v>-4.5182663108493664</v>
+      </c>
+      <c r="L103">
+        <f t="shared" si="44"/>
+        <v>-1.3023872679045105</v>
+      </c>
+      <c r="M103" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N103" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B104" t="s">
+        <v>67</v>
+      </c>
+      <c r="C104">
+        <v>57.51</v>
+      </c>
+      <c r="D104">
+        <f>VLOOKUP(B104,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.7</v>
+      </c>
+      <c r="E104">
+        <v>56.05</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="40"/>
+        <v>54.96</v>
+      </c>
+      <c r="G104" t="s">
+        <v>113</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="41"/>
+        <v>-2.5386889236654513</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="42"/>
+        <v>4.4340114762649927</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="43"/>
+        <v>-2.5386889236654513</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="44"/>
+        <v>-0.5725490196078441</v>
+      </c>
+      <c r="M104" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N104" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B105" t="s">
+        <v>243</v>
+      </c>
+      <c r="C105">
+        <v>542.04999999999995</v>
+      </c>
+      <c r="D105">
+        <f>VLOOKUP(B105,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>11.04</v>
+      </c>
+      <c r="E105">
+        <v>538</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="40"/>
+        <v>525.49</v>
+      </c>
+      <c r="G105" t="s">
+        <v>105</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="41"/>
+        <v>-0.74716354579834976</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="42"/>
+        <v>3.0550687205977209</v>
+      </c>
+      <c r="K105">
+        <f t="shared" si="43"/>
+        <v>-0.74716354579834976</v>
+      </c>
+      <c r="L105">
+        <f t="shared" si="44"/>
+        <v>-0.24456521739130241</v>
+      </c>
+      <c r="M105" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N105" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B106" t="s">
+        <v>257</v>
+      </c>
+      <c r="C106">
+        <v>28.96</v>
+      </c>
+      <c r="D106">
+        <f>VLOOKUP(B106,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.9</v>
+      </c>
+      <c r="E106">
+        <v>27.84</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="40"/>
+        <v>27.61</v>
+      </c>
+      <c r="G106" t="s">
+        <v>118</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="41"/>
+        <v>-3.8674033149171305</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="42"/>
+        <v>4.661602209944756</v>
+      </c>
+      <c r="K106">
+        <f t="shared" si="43"/>
+        <v>-3.8674033149171305</v>
+      </c>
+      <c r="L106">
+        <f t="shared" si="44"/>
+        <v>-0.82962962962962949</v>
+      </c>
+      <c r="M106" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N106" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B107" t="s">
+        <v>179</v>
+      </c>
+      <c r="C107">
+        <v>181.08</v>
+      </c>
+      <c r="D107">
+        <f>VLOOKUP(B107,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>4.13</v>
+      </c>
+      <c r="E107">
+        <v>193.53</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="40"/>
+        <v>174.88500000000002</v>
+      </c>
+      <c r="G107" t="s">
+        <v>261</v>
+      </c>
+      <c r="I107">
+        <f t="shared" si="41"/>
+        <v>6.875414181577197</v>
+      </c>
+      <c r="J107">
+        <f t="shared" si="42"/>
+        <v>3.4211398277004599</v>
+      </c>
+      <c r="K107">
+        <f t="shared" si="43"/>
+        <v>6.875414181577197</v>
+      </c>
+      <c r="L107">
+        <f t="shared" si="44"/>
+        <v>2.0096852300242136</v>
+      </c>
+      <c r="M107" t="str">
+        <f t="shared" si="45"/>
+        <v>Win</v>
+      </c>
+      <c r="N107" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B108" t="s">
+        <v>125</v>
+      </c>
+      <c r="C108">
+        <v>58.96</v>
+      </c>
+      <c r="D108">
+        <f>VLOOKUP(B108,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>2.16</v>
+      </c>
+      <c r="E108">
+        <v>55.66</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="40"/>
+        <v>55.72</v>
+      </c>
+      <c r="G108" t="s">
+        <v>176</v>
+      </c>
+      <c r="I108">
+        <f t="shared" si="41"/>
+        <v>-5.5970149253731414</v>
+      </c>
+      <c r="J108">
+        <f t="shared" si="42"/>
+        <v>5.495251017639081</v>
+      </c>
+      <c r="K108">
+        <f t="shared" si="43"/>
+        <v>-5.5970149253731414</v>
+      </c>
+      <c r="L108">
+        <f t="shared" si="44"/>
+        <v>-1.018518518518519</v>
+      </c>
+      <c r="M108" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N108" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B109" t="s">
+        <v>122</v>
+      </c>
+      <c r="C109">
+        <v>10.08</v>
+      </c>
+      <c r="D109">
+        <f>VLOOKUP(B109,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.28</v>
+      </c>
+      <c r="E109">
+        <v>9.39</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="40"/>
+        <v>8.16</v>
+      </c>
+      <c r="G109" t="s">
+        <v>113</v>
+      </c>
+      <c r="I109">
+        <f t="shared" si="41"/>
+        <v>-6.8452380952380905</v>
+      </c>
+      <c r="J109">
+        <f t="shared" si="42"/>
+        <v>19.047619047619047</v>
+      </c>
+      <c r="K109">
+        <f t="shared" si="43"/>
+        <v>-6.8452380952380905</v>
+      </c>
+      <c r="L109">
+        <f t="shared" si="44"/>
+        <v>-0.35937499999999978</v>
+      </c>
+      <c r="M109" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N109" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B110" t="s">
+        <v>67</v>
+      </c>
+      <c r="C110">
+        <v>58.52</v>
+      </c>
+      <c r="D110">
+        <f>VLOOKUP(B110,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.7</v>
+      </c>
+      <c r="E110">
+        <v>63.83</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="40"/>
+        <v>55.970000000000006</v>
+      </c>
+      <c r="G110" t="s">
+        <v>176</v>
+      </c>
+      <c r="I110">
+        <f t="shared" si="41"/>
+        <v>9.07382091592617</v>
+      </c>
+      <c r="J110">
+        <f t="shared" si="42"/>
+        <v>4.3574846206425102</v>
+      </c>
+      <c r="K110">
+        <f t="shared" si="43"/>
+        <v>9.07382091592617</v>
+      </c>
+      <c r="L110">
+        <f t="shared" si="44"/>
+        <v>2.0823529411764712</v>
+      </c>
+      <c r="M110" t="str">
+        <f t="shared" si="45"/>
+        <v>Win</v>
+      </c>
+      <c r="N110" t="s">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E23:E97">
+  <conditionalFormatting sqref="E23:E110">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$F$2=$A23</formula>
     </cfRule>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\repo_trading\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEF3C76-B35F-42F2-8591-A1E157E1C091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0BE204-A3D0-45A6-9D7B-14250DFDCDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -22,26 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="275">
   <si>
     <t>Price</t>
   </si>
@@ -847,10 +833,25 @@
     <t>bad entry for trying to anticipate the moving of the stock before showing clear signs</t>
   </si>
   <si>
-    <t>st</t>
-  </si>
-  <si>
     <t>Rally started, take a look of the momentum, and the volume, it can become a good trade</t>
+  </si>
+  <si>
+    <t>The full market is in red</t>
+  </si>
+  <si>
+    <t>The market is not favoring my trades, today VOX over 20</t>
+  </si>
+  <si>
+    <t>8 days</t>
+  </si>
+  <si>
+    <t>The stock is not showing strenght</t>
+  </si>
+  <si>
+    <t>bac</t>
+  </si>
+  <si>
+    <t>The stock was gaining momentum then it got weak by bad economic results</t>
   </si>
 </sst>
 </file>
@@ -1264,14 +1265,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
   <dimension ref="A1:I113"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F1" t="s">
         <v>60</v>
       </c>
@@ -1285,7 +1286,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1299,7 +1300,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1311,7 +1312,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1335,7 +1336,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1354,13 +1355,13 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>36.159999999999997</v>
+        <v>54.07</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1379,13 +1380,13 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>34.569999999999993</v>
+        <v>52.54</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1406,7 +1407,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1428,7 +1429,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1447,13 +1448,13 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>1.5900000000000034</v>
+        <v>1.5300000000000011</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1472,13 +1473,13 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>29.559748427672893</v>
+        <v>30.718954248365989</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1497,13 +1498,13 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>113.38495575221241</v>
+        <v>75.827630848899574</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1522,13 +1523,13 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>29.559748427672893</v>
+        <v>30.718954248365989</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1553,7 +1554,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1578,7 +1579,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1593,7 +1594,7 @@
         <v>6.81365</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1608,7 +1609,7 @@
         <v>34.765000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1623,7 +1624,7 @@
         <v>83.38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1638,7 +1639,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1653,7 +1654,7 @@
         <v>40.024999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>78.739999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>22.625</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1698,7 +1699,7 @@
         <v>2.9663500000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1713,7 +1714,7 @@
         <v>23.954999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1728,7 +1729,7 @@
         <v>2.5960000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1743,7 +1744,7 @@
         <v>15.87</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1758,7 +1759,7 @@
         <v>116.73</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1773,7 +1774,7 @@
         <v>8.7708499999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>2.73935</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -1803,7 +1804,7 @@
         <v>14.940000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>120.70000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1833,7 +1834,7 @@
         <v>6.0049999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -1848,7 +1849,7 @@
         <v>48.025000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -1863,7 +1864,7 @@
         <v>4.2656000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -1878,7 +1879,7 @@
         <v>1.099</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1893,22 +1894,22 @@
         <v>77.190000000000012</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>63</v>
       </c>
       <c r="B35">
-        <v>16.420000000000002</v>
+        <v>11.64</v>
       </c>
       <c r="C35">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="D35">
         <f>B35-(1*C35)</f>
-        <v>15.440000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -1923,7 +1924,7 @@
         <v>35.93</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -1938,7 +1939,7 @@
         <v>202.12</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -1953,7 +1954,7 @@
         <v>175.54999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1968,7 +1969,7 @@
         <v>55.85</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -1983,7 +1984,7 @@
         <v>184.095</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -1998,7 +1999,7 @@
         <v>56.785000000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2013,7 +2014,7 @@
         <v>167.73</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2028,7 +2029,7 @@
         <v>27.86</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2043,7 +2044,7 @@
         <v>12.610000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2058,7 +2059,7 @@
         <v>154.13999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2073,7 +2074,7 @@
         <v>274.39999999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2088,7 +2089,7 @@
         <v>37.975000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2103,7 +2104,7 @@
         <v>985.09</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2118,7 +2119,7 @@
         <v>5.1418999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2133,7 +2134,7 @@
         <v>56.160000000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -2148,7 +2149,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -2163,7 +2164,7 @@
         <v>174.29999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -2178,7 +2179,7 @@
         <v>15.614999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -2193,7 +2194,7 @@
         <v>7.0575000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>102</v>
       </c>
@@ -2208,7 +2209,7 @@
         <v>10.43</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>112</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>81.5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -2238,7 +2239,7 @@
         <v>128.67499999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>3.7643</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -2268,7 +2269,7 @@
         <v>100.41499999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>120</v>
       </c>
@@ -2283,7 +2284,7 @@
         <v>147.97</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>112.315</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -2313,7 +2314,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>123</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>8.0931999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -2343,7 +2344,7 @@
         <v>148.66</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>125</v>
       </c>
@@ -2358,7 +2359,7 @@
         <v>55.72</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>11.879999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>1.849</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>128</v>
       </c>
@@ -2403,7 +2404,7 @@
         <v>218.27</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>130</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>28.474999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>131</v>
       </c>
@@ -2433,7 +2434,7 @@
         <v>20.225000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>132</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>4.9234</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>134</v>
       </c>
@@ -2463,7 +2464,7 @@
         <v>123.46</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>135</v>
       </c>
@@ -2478,7 +2479,7 @@
         <v>25.119999999999997</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>136</v>
       </c>
@@ -2493,7 +2494,7 @@
         <v>150.32500000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>137</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>46.23</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>138</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v>9.2650000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>139</v>
       </c>
@@ -2538,7 +2539,7 @@
         <v>168.81</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>140</v>
       </c>
@@ -2553,7 +2554,7 @@
         <v>9.4380000000000006</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>143</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>4.7050000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>144</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v>3.7776500000000004</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>145</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>34.569999999999993</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>148</v>
       </c>
@@ -2613,7 +2614,7 @@
         <v>15.334999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>151</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>36.970000000000006</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>161</v>
       </c>
@@ -2643,7 +2644,7 @@
         <v>104.595</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>167</v>
       </c>
@@ -2658,7 +2659,7 @@
         <v>86.73</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>168</v>
       </c>
@@ -2673,7 +2674,7 @@
         <v>59.695</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>178</v>
       </c>
@@ -2688,7 +2689,7 @@
         <v>580.04</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>179</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>193.77500000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>191</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>114.71</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>192</v>
       </c>
@@ -2733,7 +2734,7 @@
         <v>22.035</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>193</v>
       </c>
@@ -2748,7 +2749,7 @@
         <v>58.625</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>194</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>19.521800000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>195</v>
       </c>
@@ -2778,7 +2779,7 @@
         <v>10.8066</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>198</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>10.688500000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>199</v>
       </c>
@@ -2808,7 +2809,7 @@
         <v>212.47500000000002</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>202</v>
       </c>
@@ -2823,7 +2824,7 @@
         <v>22.634999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>204</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>3.9053999999999998</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>207</v>
       </c>
@@ -2853,7 +2854,7 @@
         <v>314.7</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>210</v>
       </c>
@@ -2868,7 +2869,7 @@
         <v>45.964999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>212</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>73.905000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>217</v>
       </c>
@@ -2898,7 +2899,7 @@
         <v>1.3531</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>225</v>
       </c>
@@ -2913,7 +2914,7 @@
         <v>55.135000000000005</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>232</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>320.88</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>238</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>443.93</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>246</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>7.9399999999999995</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>243</v>
       </c>
@@ -2973,7 +2974,7 @@
         <v>531.01</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>247</v>
       </c>
@@ -2988,7 +2989,7 @@
         <v>52.54</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>251</v>
       </c>
@@ -3003,7 +3004,7 @@
         <v>18.835000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>255</v>
       </c>
@@ -3018,7 +3019,7 @@
         <v>87.95</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>257</v>
       </c>
@@ -3033,7 +3034,7 @@
         <v>27.619999999999997</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>263</v>
       </c>
@@ -3048,7 +3049,7 @@
         <v>32.29</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>264</v>
       </c>
@@ -3063,7 +3064,7 @@
         <v>30.81</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>266</v>
       </c>
@@ -3092,9 +3093,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A40B143-FB10-4924-B38A-19EA27551BED}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -3102,7 +3103,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3116,7 +3117,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -3133,7 +3134,7 @@
         <v>25.445292620865143</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3150,7 +3151,7 @@
         <v>5.4377379010331746</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3167,7 +3168,7 @@
         <v>90.309762485324697</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -3184,7 +3185,7 @@
         <v>18.832391713747636</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -3201,7 +3202,7 @@
         <v>141.24293785310732</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -3218,7 +3219,7 @@
         <v>57.471264367816147</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -3235,7 +3236,7 @@
         <v>37.878787878787868</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -3252,7 +3253,7 @@
         <v>62.786463238525748</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -3269,7 +3270,7 @@
         <v>5.4764512595837926</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -3286,7 +3287,7 @@
         <v>42.194092827004262</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -3310,29 +3311,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2A77BB-0F93-4C87-9B0A-B8954405005E}">
-  <dimension ref="A1:N110"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N114"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="101.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
+    <col min="14" max="14" width="101.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="3">
         <f>COUNTIF(M:M,"Win")/COUNTA(M:M)</f>
-        <v>0.48039215686274511</v>
+        <v>0.46226415094339623</v>
       </c>
       <c r="C1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -3341,34 +3342,34 @@
         <v>9.7235064318751352</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
       <c r="B3">
         <f>AVERAGEIF(M:M,"Loss",I:I)</f>
-        <v>-4.3531092320495279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-4.340372317043248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>95</v>
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.36974810813780523</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.32996216034162468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
       <c r="B5">
         <f>(B1*B2+(1-B1)*B3)</f>
-        <v>2.4091865280711442</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2.1608546517963823</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -3412,7 +3413,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45972</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45941</v>
       </c>
@@ -3515,7 +3516,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45973</v>
       </c>
@@ -3566,7 +3567,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45974</v>
       </c>
@@ -3617,7 +3618,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45974</v>
       </c>
@@ -3668,7 +3669,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45974</v>
       </c>
@@ -3716,7 +3717,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45975</v>
       </c>
@@ -3764,7 +3765,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45978</v>
       </c>
@@ -3812,7 +3813,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45978</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45979</v>
       </c>
@@ -3908,7 +3909,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>45979</v>
       </c>
@@ -3956,7 +3957,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>45979</v>
       </c>
@@ -4004,7 +4005,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>45980</v>
       </c>
@@ -4052,7 +4053,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>45981</v>
       </c>
@@ -4100,7 +4101,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>45981</v>
       </c>
@@ -4145,7 +4146,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>45981</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>45986</v>
       </c>
@@ -4238,7 +4239,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>45987</v>
       </c>
@@ -4286,7 +4287,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>45987</v>
       </c>
@@ -4334,7 +4335,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>45992</v>
       </c>
@@ -4382,7 +4383,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>45993</v>
       </c>
@@ -4430,7 +4431,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>45993</v>
       </c>
@@ -4478,7 +4479,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>45993</v>
       </c>
@@ -4526,7 +4527,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>45993</v>
       </c>
@@ -4574,7 +4575,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>45993</v>
       </c>
@@ -4622,7 +4623,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>45993</v>
       </c>
@@ -4670,7 +4671,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>45993</v>
       </c>
@@ -4718,7 +4719,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>45993</v>
       </c>
@@ -4766,7 +4767,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>45995</v>
       </c>
@@ -4814,7 +4815,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>45995</v>
       </c>
@@ -4862,7 +4863,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>45996</v>
       </c>
@@ -4910,7 +4911,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>45996</v>
       </c>
@@ -4958,7 +4959,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>45996</v>
       </c>
@@ -5006,7 +5007,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>45999</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>45999</v>
       </c>
@@ -5102,7 +5103,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>45999</v>
       </c>
@@ -5150,7 +5151,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>46000</v>
       </c>
@@ -5198,7 +5199,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46000</v>
       </c>
@@ -5246,7 +5247,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>46000</v>
       </c>
@@ -5294,7 +5295,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>46003</v>
       </c>
@@ -5342,7 +5343,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>46003</v>
       </c>
@@ -5387,7 +5388,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>46007</v>
       </c>
@@ -5435,7 +5436,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>46007</v>
       </c>
@@ -5483,7 +5484,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>46008</v>
       </c>
@@ -5531,7 +5532,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>46008</v>
       </c>
@@ -5579,7 +5580,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>46008</v>
       </c>
@@ -5627,7 +5628,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>46008</v>
       </c>
@@ -5675,7 +5676,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>46008</v>
       </c>
@@ -5723,7 +5724,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>46009</v>
       </c>
@@ -5771,7 +5772,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>46010</v>
       </c>
@@ -5819,7 +5820,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>46014</v>
       </c>
@@ -5867,7 +5868,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>46024</v>
       </c>
@@ -5915,7 +5916,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>46027</v>
       </c>
@@ -5963,7 +5964,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>46028</v>
       </c>
@@ -6011,7 +6012,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>46029</v>
       </c>
@@ -6059,7 +6060,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>46030</v>
       </c>
@@ -6107,7 +6108,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>46030</v>
       </c>
@@ -6155,7 +6156,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>46034</v>
       </c>
@@ -6203,7 +6204,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>46034</v>
       </c>
@@ -6251,7 +6252,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>46036</v>
       </c>
@@ -6299,7 +6300,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>46038</v>
       </c>
@@ -6347,7 +6348,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>46038</v>
       </c>
@@ -6395,7 +6396,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>46042</v>
       </c>
@@ -6443,7 +6444,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>46042</v>
       </c>
@@ -6491,7 +6492,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>46042</v>
       </c>
@@ -6539,7 +6540,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>46043</v>
       </c>
@@ -6587,7 +6588,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>46044</v>
       </c>
@@ -6635,7 +6636,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>46044</v>
       </c>
@@ -6683,7 +6684,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>46044</v>
       </c>
@@ -6731,7 +6732,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>46045</v>
       </c>
@@ -6779,7 +6780,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>46045</v>
       </c>
@@ -6827,7 +6828,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>46045</v>
       </c>
@@ -6875,7 +6876,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>46048</v>
       </c>
@@ -6923,7 +6924,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>46049</v>
       </c>
@@ -6971,7 +6972,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>46049</v>
       </c>
@@ -7019,7 +7020,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>46049</v>
       </c>
@@ -7067,7 +7068,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>46049</v>
       </c>
@@ -7115,7 +7116,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>46049</v>
       </c>
@@ -7163,7 +7164,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>46050</v>
       </c>
@@ -7211,7 +7212,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>46050</v>
       </c>
@@ -7229,7 +7230,7 @@
         <v>327.12</v>
       </c>
       <c r="F89">
-        <f t="shared" ref="F89:F110" si="40">C89-(1.5*D89)</f>
+        <f t="shared" ref="F89:F114" si="40">C89-(1.5*D89)</f>
         <v>314.98500000000001</v>
       </c>
       <c r="G89" t="s">
@@ -7259,7 +7260,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>46050</v>
       </c>
@@ -7307,7 +7308,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>46050</v>
       </c>
@@ -7355,7 +7356,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>46051</v>
       </c>
@@ -7403,7 +7404,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>46051</v>
       </c>
@@ -7428,30 +7429,30 @@
         <v>118</v>
       </c>
       <c r="I93">
-        <f t="shared" ref="I93:I110" si="41">(E93-C93)/C93*(100)</f>
+        <f t="shared" ref="I93:I114" si="41">(E93-C93)/C93*(100)</f>
         <v>-0.69353228602953898</v>
       </c>
       <c r="J93">
-        <f t="shared" ref="J93:J110" si="42">(C93-F93)/C93*100</f>
+        <f t="shared" ref="J93:J114" si="42">(C93-F93)/C93*100</f>
         <v>4.0272158881941849</v>
       </c>
       <c r="K93">
-        <f t="shared" ref="K93:K110" si="43">(E93-C93)/C93*100</f>
+        <f t="shared" ref="K93:K114" si="43">(E93-C93)/C93*100</f>
         <v>-0.69353228602953898</v>
       </c>
       <c r="L93">
-        <f t="shared" ref="L93:L110" si="44">K93/J93</f>
+        <f t="shared" ref="L93:L114" si="44">K93/J93</f>
         <v>-0.17221135029354506</v>
       </c>
       <c r="M93" t="str">
-        <f t="shared" ref="M93:M110" si="45">IF(I93&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M93:M114" si="45">IF(I93&gt;0,"Win","Loss")</f>
         <v>Loss</v>
       </c>
       <c r="N93" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>46051</v>
       </c>
@@ -7499,7 +7500,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>46051</v>
       </c>
@@ -7547,7 +7548,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>46052</v>
       </c>
@@ -7595,7 +7596,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>46055</v>
       </c>
@@ -7643,7 +7644,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>46056</v>
       </c>
@@ -7691,7 +7692,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>46056</v>
       </c>
@@ -7739,7 +7740,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>46057</v>
       </c>
@@ -7787,7 +7788,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>46057</v>
       </c>
@@ -7835,7 +7836,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>46057</v>
       </c>
@@ -7883,7 +7884,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>46058</v>
       </c>
@@ -7931,7 +7932,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>46058</v>
       </c>
@@ -7979,7 +7980,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>46062</v>
       </c>
@@ -8027,7 +8028,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>46062</v>
       </c>
@@ -8075,7 +8076,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>46063</v>
       </c>
@@ -8123,7 +8124,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>46063</v>
       </c>
@@ -8171,7 +8172,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>46064</v>
       </c>
@@ -8219,7 +8220,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>46064</v>
       </c>
@@ -8264,12 +8265,204 @@
         <v>Win</v>
       </c>
       <c r="N110" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B111" t="s">
+        <v>63</v>
+      </c>
+      <c r="C111">
+        <v>11.64</v>
+      </c>
+      <c r="D111">
+        <f>VLOOKUP(B111,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.84</v>
+      </c>
+      <c r="E111">
+        <v>11.29</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="40"/>
+        <v>10.38</v>
+      </c>
+      <c r="G111" t="s">
+        <v>113</v>
+      </c>
+      <c r="I111">
+        <f t="shared" si="41"/>
+        <v>-3.0068728522336894</v>
+      </c>
+      <c r="J111">
+        <f t="shared" si="42"/>
+        <v>10.824742268041234</v>
+      </c>
+      <c r="K111">
+        <f t="shared" si="43"/>
+        <v>-3.0068728522336894</v>
+      </c>
+      <c r="L111">
+        <f t="shared" si="44"/>
+        <v>-0.27777777777777901</v>
+      </c>
+      <c r="M111" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N111" t="s">
         <v>269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="s">
+        <v>264</v>
+      </c>
+      <c r="C112">
+        <v>33.93</v>
+      </c>
+      <c r="D112">
+        <f>VLOOKUP(B112,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>2.08</v>
+      </c>
+      <c r="E112">
+        <v>31.3</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="40"/>
+        <v>30.81</v>
+      </c>
+      <c r="G112" t="s">
+        <v>176</v>
+      </c>
+      <c r="I112">
+        <f t="shared" si="41"/>
+        <v>-7.7512525788387823</v>
+      </c>
+      <c r="J112">
+        <f t="shared" si="42"/>
+        <v>9.1954022988505777</v>
+      </c>
+      <c r="K112">
+        <f t="shared" si="43"/>
+        <v>-7.7512525788387823</v>
+      </c>
+      <c r="L112">
+        <f t="shared" si="44"/>
+        <v>-0.84294871794871729</v>
+      </c>
+      <c r="M112" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N112" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B113" t="s">
+        <v>255</v>
+      </c>
+      <c r="C113">
+        <v>92.18</v>
+      </c>
+      <c r="D113">
+        <f>VLOOKUP(B113,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>2.82</v>
+      </c>
+      <c r="E113">
+        <v>88.63</v>
+      </c>
+      <c r="F113">
+        <f t="shared" si="40"/>
+        <v>87.95</v>
+      </c>
+      <c r="G113" t="s">
+        <v>271</v>
+      </c>
+      <c r="I113">
+        <f t="shared" si="41"/>
+        <v>-3.8511607724018351</v>
+      </c>
+      <c r="J113">
+        <f t="shared" si="42"/>
+        <v>4.5888479062703453</v>
+      </c>
+      <c r="K113">
+        <f t="shared" si="43"/>
+        <v>-3.8511607724018351</v>
+      </c>
+      <c r="L113">
+        <f t="shared" si="44"/>
+        <v>-0.83924349881796878</v>
+      </c>
+      <c r="M113" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N113" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B114" t="s">
+        <v>247</v>
+      </c>
+      <c r="C114">
+        <v>54.07</v>
+      </c>
+      <c r="D114">
+        <f>VLOOKUP(B114,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.02</v>
+      </c>
+      <c r="E114">
+        <v>52.94</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="40"/>
+        <v>52.54</v>
+      </c>
+      <c r="G114" t="s">
+        <v>271</v>
+      </c>
+      <c r="I114">
+        <f t="shared" si="41"/>
+        <v>-2.0898834843721148</v>
+      </c>
+      <c r="J114">
+        <f t="shared" si="42"/>
+        <v>2.8296652487516205</v>
+      </c>
+      <c r="K114">
+        <f t="shared" si="43"/>
+        <v>-2.0898834843721148</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="44"/>
+        <v>-0.73856209150326901</v>
+      </c>
+      <c r="M114" t="str">
+        <f t="shared" si="45"/>
+        <v>Loss</v>
+      </c>
+      <c r="N114" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E23:E110">
+  <conditionalFormatting sqref="E23:E114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$F$2=$A23</formula>
     </cfRule>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\repo_trading\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0BE204-A3D0-45A6-9D7B-14250DFDCDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BC7A48-7AB7-41DC-ADC9-14781119BE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,20 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -848,10 +862,10 @@
     <t>The stock is not showing strenght</t>
   </si>
   <si>
-    <t>bac</t>
-  </si>
-  <si>
     <t>The stock was gaining momentum then it got weak by bad economic results</t>
+  </si>
+  <si>
+    <t>pfe</t>
   </si>
 </sst>
 </file>
@@ -1265,14 +1279,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
   <dimension ref="A1:I113"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F1" t="s">
         <v>60</v>
       </c>
@@ -1286,7 +1300,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1300,7 +1314,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1312,7 +1326,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1336,7 +1350,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1355,13 +1369,13 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>54.07</v>
+        <v>27.83</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1380,13 +1394,13 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>52.54</v>
+        <v>26.884999999999998</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1407,7 +1421,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1429,7 +1443,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1448,13 +1462,13 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>1.5300000000000011</v>
+        <v>0.94500000000000028</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1473,13 +1487,13 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>30.718954248365989</v>
+        <v>49.73544973544972</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1498,13 +1512,13 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>75.827630848899574</v>
+        <v>147.32303269852679</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1523,13 +1537,13 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>30.718954248365989</v>
+        <v>49.73544973544972</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1554,7 +1568,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1579,7 +1593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1594,7 +1608,7 @@
         <v>6.81365</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1609,7 +1623,7 @@
         <v>34.765000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1624,7 +1638,7 @@
         <v>83.38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1639,7 +1653,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1654,7 +1668,7 @@
         <v>40.024999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1669,7 +1683,7 @@
         <v>78.739999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1684,7 +1698,7 @@
         <v>22.625</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1699,7 +1713,7 @@
         <v>2.9663500000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1714,7 +1728,7 @@
         <v>23.954999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1729,7 +1743,7 @@
         <v>2.5960000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1744,7 +1758,7 @@
         <v>15.87</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1759,7 +1773,7 @@
         <v>116.73</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1774,7 +1788,7 @@
         <v>8.7708499999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1789,7 +1803,7 @@
         <v>2.73935</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -1804,7 +1818,7 @@
         <v>14.940000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -1819,7 +1833,7 @@
         <v>120.70000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1834,7 +1848,7 @@
         <v>6.0049999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -1849,7 +1863,7 @@
         <v>48.025000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -1864,7 +1878,7 @@
         <v>4.2656000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -1879,7 +1893,7 @@
         <v>1.099</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1894,7 +1908,7 @@
         <v>77.190000000000012</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -1909,7 +1923,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -1924,7 +1938,7 @@
         <v>35.93</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -1939,7 +1953,7 @@
         <v>202.12</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -1954,7 +1968,7 @@
         <v>175.54999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1969,7 +1983,7 @@
         <v>55.85</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -1984,7 +1998,7 @@
         <v>184.095</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -1999,7 +2013,7 @@
         <v>56.785000000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2014,7 +2028,7 @@
         <v>167.73</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2029,7 +2043,7 @@
         <v>27.86</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2044,7 +2058,7 @@
         <v>12.610000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2059,7 +2073,7 @@
         <v>154.13999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2074,7 +2088,7 @@
         <v>274.39999999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2089,7 +2103,7 @@
         <v>37.975000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2104,7 +2118,7 @@
         <v>985.09</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2119,7 +2133,7 @@
         <v>5.1418999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2134,7 +2148,7 @@
         <v>56.160000000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -2149,7 +2163,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -2164,7 +2178,7 @@
         <v>174.29999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -2179,7 +2193,7 @@
         <v>15.614999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -2194,7 +2208,7 @@
         <v>7.0575000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>102</v>
       </c>
@@ -2209,7 +2223,7 @@
         <v>10.43</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>112</v>
       </c>
@@ -2224,7 +2238,7 @@
         <v>81.5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -2239,7 +2253,7 @@
         <v>128.67499999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2254,7 +2268,7 @@
         <v>3.7643</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -2269,7 +2283,7 @@
         <v>100.41499999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>120</v>
       </c>
@@ -2284,7 +2298,7 @@
         <v>147.97</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2299,7 +2313,7 @@
         <v>112.315</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -2314,7 +2328,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>123</v>
       </c>
@@ -2329,7 +2343,7 @@
         <v>8.0931999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -2344,7 +2358,7 @@
         <v>148.66</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>125</v>
       </c>
@@ -2359,7 +2373,7 @@
         <v>55.72</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -2374,7 +2388,7 @@
         <v>11.879999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -2389,7 +2403,7 @@
         <v>1.849</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>128</v>
       </c>
@@ -2404,7 +2418,7 @@
         <v>218.27</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>130</v>
       </c>
@@ -2419,7 +2433,7 @@
         <v>28.474999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>131</v>
       </c>
@@ -2434,7 +2448,7 @@
         <v>20.225000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>132</v>
       </c>
@@ -2449,7 +2463,7 @@
         <v>4.9234</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>134</v>
       </c>
@@ -2464,22 +2478,22 @@
         <v>123.46</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>135</v>
       </c>
       <c r="B73">
-        <v>26.08</v>
+        <v>27.83</v>
       </c>
       <c r="C73">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="D73">
         <f>B73-(1.5*C73)</f>
-        <v>25.119999999999997</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+        <v>26.884999999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>136</v>
       </c>
@@ -2494,7 +2508,7 @@
         <v>150.32500000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>137</v>
       </c>
@@ -2509,7 +2523,7 @@
         <v>46.23</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>138</v>
       </c>
@@ -2524,7 +2538,7 @@
         <v>9.2650000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>139</v>
       </c>
@@ -2539,7 +2553,7 @@
         <v>168.81</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>140</v>
       </c>
@@ -2554,7 +2568,7 @@
         <v>9.4380000000000006</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>143</v>
       </c>
@@ -2569,7 +2583,7 @@
         <v>4.7050000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>144</v>
       </c>
@@ -2584,7 +2598,7 @@
         <v>3.7776500000000004</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>145</v>
       </c>
@@ -2599,7 +2613,7 @@
         <v>34.569999999999993</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>148</v>
       </c>
@@ -2614,7 +2628,7 @@
         <v>15.334999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>151</v>
       </c>
@@ -2629,7 +2643,7 @@
         <v>36.970000000000006</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>161</v>
       </c>
@@ -2644,7 +2658,7 @@
         <v>104.595</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>167</v>
       </c>
@@ -2659,7 +2673,7 @@
         <v>86.73</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>168</v>
       </c>
@@ -2674,7 +2688,7 @@
         <v>59.695</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>178</v>
       </c>
@@ -2689,7 +2703,7 @@
         <v>580.04</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>179</v>
       </c>
@@ -2704,7 +2718,7 @@
         <v>193.77500000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>191</v>
       </c>
@@ -2719,7 +2733,7 @@
         <v>114.71</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>192</v>
       </c>
@@ -2734,7 +2748,7 @@
         <v>22.035</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>193</v>
       </c>
@@ -2749,7 +2763,7 @@
         <v>58.625</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>194</v>
       </c>
@@ -2764,7 +2778,7 @@
         <v>19.521800000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>195</v>
       </c>
@@ -2779,7 +2793,7 @@
         <v>10.8066</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>198</v>
       </c>
@@ -2794,7 +2808,7 @@
         <v>10.688500000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>199</v>
       </c>
@@ -2809,7 +2823,7 @@
         <v>212.47500000000002</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>202</v>
       </c>
@@ -2824,7 +2838,7 @@
         <v>22.634999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>204</v>
       </c>
@@ -2839,7 +2853,7 @@
         <v>3.9053999999999998</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>207</v>
       </c>
@@ -2854,7 +2868,7 @@
         <v>314.7</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>210</v>
       </c>
@@ -2869,7 +2883,7 @@
         <v>45.964999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>212</v>
       </c>
@@ -2884,7 +2898,7 @@
         <v>73.905000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>217</v>
       </c>
@@ -2899,7 +2913,7 @@
         <v>1.3531</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>225</v>
       </c>
@@ -2914,7 +2928,7 @@
         <v>55.135000000000005</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>232</v>
       </c>
@@ -2929,7 +2943,7 @@
         <v>320.88</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>238</v>
       </c>
@@ -2944,7 +2958,7 @@
         <v>443.93</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>246</v>
       </c>
@@ -2959,7 +2973,7 @@
         <v>7.9399999999999995</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>243</v>
       </c>
@@ -2974,7 +2988,7 @@
         <v>531.01</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>247</v>
       </c>
@@ -2989,7 +3003,7 @@
         <v>52.54</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>251</v>
       </c>
@@ -3004,7 +3018,7 @@
         <v>18.835000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>255</v>
       </c>
@@ -3019,7 +3033,7 @@
         <v>87.95</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>257</v>
       </c>
@@ -3034,7 +3048,7 @@
         <v>27.619999999999997</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>263</v>
       </c>
@@ -3049,7 +3063,7 @@
         <v>32.29</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>264</v>
       </c>
@@ -3064,7 +3078,7 @@
         <v>30.81</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>266</v>
       </c>
@@ -3093,9 +3107,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A40B143-FB10-4924-B38A-19EA27551BED}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -3103,7 +3117,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3117,7 +3131,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -3134,7 +3148,7 @@
         <v>25.445292620865143</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3151,7 +3165,7 @@
         <v>5.4377379010331746</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3168,7 +3182,7 @@
         <v>90.309762485324697</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -3185,7 +3199,7 @@
         <v>18.832391713747636</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -3202,7 +3216,7 @@
         <v>141.24293785310732</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -3219,7 +3233,7 @@
         <v>57.471264367816147</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -3236,7 +3250,7 @@
         <v>37.878787878787868</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -3253,7 +3267,7 @@
         <v>62.786463238525748</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -3270,7 +3284,7 @@
         <v>5.4764512595837926</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -3287,7 +3301,7 @@
         <v>42.194092827004262</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -3312,16 +3326,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2A77BB-0F93-4C87-9B0A-B8954405005E}">
   <dimension ref="A1:N114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" customWidth="1"/>
-    <col min="14" max="14" width="101.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="14" max="14" width="101.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -3333,7 +3347,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -3342,7 +3356,7 @@
         <v>9.7235064318751352</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -3351,16 +3365,16 @@
         <v>-4.340372317043248</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>95</v>
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.32996216034162468</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0.3298109887618817</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -3369,7 +3383,7 @@
         <v>2.1608546517963823</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -3413,7 +3427,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45972</v>
       </c>
@@ -3464,7 +3478,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45941</v>
       </c>
@@ -3516,7 +3530,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45973</v>
       </c>
@@ -3567,7 +3581,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45974</v>
       </c>
@@ -3618,7 +3632,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45974</v>
       </c>
@@ -3669,7 +3683,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45974</v>
       </c>
@@ -3717,7 +3731,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45975</v>
       </c>
@@ -3765,7 +3779,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45978</v>
       </c>
@@ -3813,7 +3827,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45978</v>
       </c>
@@ -3861,7 +3875,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45979</v>
       </c>
@@ -3909,7 +3923,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45979</v>
       </c>
@@ -3957,7 +3971,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>45979</v>
       </c>
@@ -4005,7 +4019,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45980</v>
       </c>
@@ -4053,7 +4067,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45981</v>
       </c>
@@ -4101,7 +4115,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45981</v>
       </c>
@@ -4146,7 +4160,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45981</v>
       </c>
@@ -4191,7 +4205,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45986</v>
       </c>
@@ -4239,7 +4253,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>45987</v>
       </c>
@@ -4287,7 +4301,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>45987</v>
       </c>
@@ -4335,7 +4349,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>45992</v>
       </c>
@@ -4383,7 +4397,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>45993</v>
       </c>
@@ -4431,7 +4445,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45993</v>
       </c>
@@ -4479,7 +4493,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45993</v>
       </c>
@@ -4527,7 +4541,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>45993</v>
       </c>
@@ -4575,7 +4589,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>45993</v>
       </c>
@@ -4623,7 +4637,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>45993</v>
       </c>
@@ -4671,7 +4685,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>45993</v>
       </c>
@@ -4719,7 +4733,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45993</v>
       </c>
@@ -4767,7 +4781,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>45995</v>
       </c>
@@ -4815,7 +4829,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>45995</v>
       </c>
@@ -4863,7 +4877,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>45996</v>
       </c>
@@ -4911,7 +4925,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>45996</v>
       </c>
@@ -4959,7 +4973,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>45996</v>
       </c>
@@ -5007,7 +5021,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45999</v>
       </c>
@@ -5055,7 +5069,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>45999</v>
       </c>
@@ -5103,7 +5117,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45999</v>
       </c>
@@ -5151,7 +5165,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46000</v>
       </c>
@@ -5199,7 +5213,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46000</v>
       </c>
@@ -5247,7 +5261,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>46000</v>
       </c>
@@ -5295,7 +5309,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46003</v>
       </c>
@@ -5343,7 +5357,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46003</v>
       </c>
@@ -5388,7 +5402,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>46007</v>
       </c>
@@ -5436,7 +5450,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>46007</v>
       </c>
@@ -5448,14 +5462,14 @@
       </c>
       <c r="D52">
         <f>VLOOKUP(B52,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="E52">
         <v>25.12</v>
       </c>
       <c r="F52">
         <f t="shared" si="5"/>
-        <v>25.119999999999997</v>
+        <v>25.134999999999998</v>
       </c>
       <c r="G52" t="s">
         <v>105</v>
@@ -5466,7 +5480,7 @@
       </c>
       <c r="J52">
         <f t="shared" si="26"/>
-        <v>3.6809815950920282</v>
+        <v>3.6234662576687131</v>
       </c>
       <c r="K52">
         <f t="shared" si="27"/>
@@ -5474,7 +5488,7 @@
       </c>
       <c r="L52">
         <f t="shared" si="28"/>
-        <v>-0.99999999999999623</v>
+        <v>-1.0158730158730127</v>
       </c>
       <c r="M52" t="str">
         <f t="shared" si="29"/>
@@ -5484,7 +5498,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>46008</v>
       </c>
@@ -5532,7 +5546,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>46008</v>
       </c>
@@ -5580,7 +5594,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>46008</v>
       </c>
@@ -5628,7 +5642,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>46008</v>
       </c>
@@ -5676,7 +5690,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>46008</v>
       </c>
@@ -5724,7 +5738,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>46009</v>
       </c>
@@ -5772,7 +5786,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>46010</v>
       </c>
@@ -5820,7 +5834,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>46014</v>
       </c>
@@ -5868,7 +5882,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>46024</v>
       </c>
@@ -5916,7 +5930,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>46027</v>
       </c>
@@ -5964,7 +5978,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>46028</v>
       </c>
@@ -6012,7 +6026,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>46029</v>
       </c>
@@ -6060,7 +6074,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>46030</v>
       </c>
@@ -6108,7 +6122,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>46030</v>
       </c>
@@ -6156,7 +6170,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>46034</v>
       </c>
@@ -6204,7 +6218,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>46034</v>
       </c>
@@ -6252,7 +6266,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>46036</v>
       </c>
@@ -6300,7 +6314,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>46038</v>
       </c>
@@ -6348,7 +6362,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>46038</v>
       </c>
@@ -6396,7 +6410,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>46042</v>
       </c>
@@ -6444,7 +6458,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>46042</v>
       </c>
@@ -6492,7 +6506,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>46042</v>
       </c>
@@ -6540,7 +6554,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>46043</v>
       </c>
@@ -6588,7 +6602,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>46044</v>
       </c>
@@ -6636,7 +6650,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>46044</v>
       </c>
@@ -6684,7 +6698,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>46044</v>
       </c>
@@ -6732,7 +6746,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>46045</v>
       </c>
@@ -6780,7 +6794,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>46045</v>
       </c>
@@ -6828,7 +6842,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>46045</v>
       </c>
@@ -6876,7 +6890,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>46048</v>
       </c>
@@ -6924,7 +6938,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>46049</v>
       </c>
@@ -6972,7 +6986,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>46049</v>
       </c>
@@ -7020,7 +7034,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>46049</v>
       </c>
@@ -7068,7 +7082,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>46049</v>
       </c>
@@ -7116,7 +7130,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>46049</v>
       </c>
@@ -7164,7 +7178,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>46050</v>
       </c>
@@ -7212,7 +7226,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>46050</v>
       </c>
@@ -7260,7 +7274,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>46050</v>
       </c>
@@ -7308,7 +7322,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>46050</v>
       </c>
@@ -7356,7 +7370,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>46051</v>
       </c>
@@ -7404,7 +7418,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>46051</v>
       </c>
@@ -7452,7 +7466,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>46051</v>
       </c>
@@ -7500,7 +7514,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>46051</v>
       </c>
@@ -7548,7 +7562,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>46052</v>
       </c>
@@ -7596,7 +7610,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>46055</v>
       </c>
@@ -7644,7 +7658,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>46056</v>
       </c>
@@ -7692,7 +7706,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>46056</v>
       </c>
@@ -7740,7 +7754,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>46057</v>
       </c>
@@ -7788,7 +7802,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>46057</v>
       </c>
@@ -7836,7 +7850,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>46057</v>
       </c>
@@ -7884,7 +7898,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>46058</v>
       </c>
@@ -7932,7 +7946,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>46058</v>
       </c>
@@ -7980,7 +7994,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>46062</v>
       </c>
@@ -8028,7 +8042,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>46062</v>
       </c>
@@ -8076,7 +8090,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>46063</v>
       </c>
@@ -8124,7 +8138,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>46063</v>
       </c>
@@ -8172,7 +8186,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>46064</v>
       </c>
@@ -8220,7 +8234,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>46064</v>
       </c>
@@ -8268,7 +8282,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>46065</v>
       </c>
@@ -8316,7 +8330,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>46065</v>
       </c>
@@ -8364,7 +8378,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>46065</v>
       </c>
@@ -8412,7 +8426,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>46065</v>
       </c>
@@ -8457,7 +8471,7 @@
         <v>Loss</v>
       </c>
       <c r="N114" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BC7A48-7AB7-41DC-ADC9-14781119BE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E22CE8F-5495-42E5-BDAE-DF1C874C4017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Results" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="300">
   <si>
     <t>Price</t>
   </si>
@@ -865,7 +866,82 @@
     <t>The stock was gaining momentum then it got weak by bad economic results</t>
   </si>
   <si>
-    <t>pfe</t>
+    <t>possible cup handle pattern formed, rejected</t>
+  </si>
+  <si>
+    <t>UNH</t>
+  </si>
+  <si>
+    <t>LFS</t>
+  </si>
+  <si>
+    <t>sold half for reducing position since tomorrow there is earnings release</t>
+  </si>
+  <si>
+    <t>Stopped out during strong big move</t>
+  </si>
+  <si>
+    <t>Sold, position, the stock didn't move the way it was expected, after finding a resistance in the same levels where I bought</t>
+  </si>
+  <si>
+    <t>6 days</t>
+  </si>
+  <si>
+    <t>Sold in strenght before earnings release</t>
+  </si>
+  <si>
+    <t>Sold with small loss before earnings, yesterday partially sold, but todays shows more weakness</t>
+  </si>
+  <si>
+    <t>It is showing lateral negative move, it is not increasing despite MACD in green</t>
+  </si>
+  <si>
+    <t>SATS</t>
+  </si>
+  <si>
+    <t>MACD turned to green but there was no follow up and it went back to red</t>
+  </si>
+  <si>
+    <t>It showed rejection at 65 levels and buyers couldn't defend it, it got weak</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>Sold on strenght</t>
+  </si>
+  <si>
+    <t>Sold before earnings announcement for reducing risk and secure profit. Bad timing for entry</t>
+  </si>
+  <si>
+    <t>QUBT</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>QBTS</t>
+  </si>
+  <si>
+    <t>OKLO</t>
+  </si>
+  <si>
+    <t>26 days</t>
+  </si>
+  <si>
+    <t>Sold on strenght, volatility has spiked up, and the stock loss momentum</t>
+  </si>
+  <si>
+    <t>Stopped out after long lateral move, today's volatility finally took me out. Bad trade</t>
+  </si>
+  <si>
+    <t>Stopped out during selloff caused by new war</t>
+  </si>
+  <si>
+    <t>Stopped out during war volatility</t>
+  </si>
+  <si>
+    <t>tmdx</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -1314,13 +1390,13 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
       <c r="H2">
-        <v>9400</v>
+        <v>8000</v>
       </c>
       <c r="I2" t="s">
         <v>27</v>
@@ -1344,7 +1420,7 @@
         <v>43</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I3" t="s">
         <v>27</v>
@@ -1369,7 +1445,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>27.83</v>
+        <v>137.27000000000001</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1394,7 +1470,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>26.884999999999998</v>
+        <v>127.61000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1418,7 +1494,7 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>4100</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1426,21 +1502,21 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>20.38</v>
+        <v>22.46</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>16.63</v>
+        <v>19.355</v>
       </c>
       <c r="G7" t="s">
         <v>48</v>
       </c>
       <c r="H7">
         <f>$H$2*(H3/100)</f>
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1462,7 +1538,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>0.94500000000000028</v>
+        <v>9.6599999999999966</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1487,7 +1563,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>49.73544973544972</v>
+        <v>2.0703933747412018</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1512,7 +1588,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>147.32303269852679</v>
+        <v>36.424564726451514</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1537,7 +1613,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>49.73544973544972</v>
+        <v>2.0703933747412018</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1562,7 +1638,7 @@
       </c>
       <c r="H12">
         <f>(H4-H5)*H11</f>
-        <v>47</v>
+        <v>20.000000000000004</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
@@ -1587,7 +1663,7 @@
       </c>
       <c r="H13">
         <f>(H12/H2)*100</f>
-        <v>0.5</v>
+        <v>0.25000000000000006</v>
       </c>
       <c r="I13" t="s">
         <v>42</v>
@@ -1628,14 +1704,14 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>91.33</v>
+        <v>88.58</v>
       </c>
       <c r="C16">
-        <v>5.3</v>
+        <v>7.63</v>
       </c>
       <c r="D16">
-        <f t="shared" si="0"/>
-        <v>83.38</v>
+        <f>B16-(1*C16)</f>
+        <v>80.95</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1733,14 +1809,14 @@
         <v>50</v>
       </c>
       <c r="B23">
-        <v>2.95</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C23">
-        <v>0.23599999999999999</v>
+        <v>0.2452</v>
       </c>
       <c r="D23">
-        <f t="shared" si="0"/>
-        <v>2.5960000000000001</v>
+        <f>B23-(1*C23)</f>
+        <v>3.9448000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,14 +1869,14 @@
         <v>54</v>
       </c>
       <c r="B27">
-        <v>3.17</v>
+        <v>2.15</v>
       </c>
       <c r="C27">
-        <v>0.28710000000000002</v>
+        <v>0.192</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>2.73935</v>
+        <v>1.8619999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1838,14 +1914,14 @@
         <v>57</v>
       </c>
       <c r="B30">
-        <v>6.32</v>
+        <v>8.99</v>
       </c>
       <c r="C30">
-        <v>0.21</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D30">
         <f t="shared" si="0"/>
-        <v>6.0049999999999999</v>
+        <v>8.1650000000000009</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2123,14 +2199,14 @@
         <v>77</v>
       </c>
       <c r="B49">
-        <v>6.02</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="C49">
-        <v>0.58540000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="D49">
         <f>B49-(1.5*C49)</f>
-        <v>5.1418999999999997</v>
+        <v>3.7449999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2273,14 +2349,14 @@
         <v>116</v>
       </c>
       <c r="B59">
-        <v>106.85</v>
+        <v>92.5</v>
       </c>
       <c r="C59">
-        <v>4.29</v>
+        <v>4.78</v>
       </c>
       <c r="D59">
-        <f>B59-(1.5*C59)</f>
-        <v>100.41499999999999</v>
+        <f>B59-(1*C59)</f>
+        <v>87.72</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2318,14 +2394,14 @@
         <v>122</v>
       </c>
       <c r="B62">
-        <v>10.08</v>
+        <v>10.58</v>
       </c>
       <c r="C62">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="D62">
         <f>B62-(1*C62)</f>
-        <v>8.8000000000000007</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2333,14 +2409,14 @@
         <v>123</v>
       </c>
       <c r="B63">
-        <v>9.09</v>
+        <v>10.37</v>
       </c>
       <c r="C63">
-        <v>0.49840000000000001</v>
+        <v>0.91759999999999997</v>
       </c>
       <c r="D63">
-        <f>B63-(2*C63)</f>
-        <v>8.0931999999999995</v>
+        <f>B63-(1*C63)</f>
+        <v>9.452399999999999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2378,14 +2454,14 @@
         <v>126</v>
       </c>
       <c r="B66">
-        <v>12.92</v>
+        <v>15.63</v>
       </c>
       <c r="C66">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="D66">
-        <f>B66-(1*C66)</f>
-        <v>11.879999999999999</v>
+        <f>B66-(1.5*C66)</f>
+        <v>13.71</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2399,7 +2475,7 @@
         <v>0.1605</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D71" si="2">B67-(2*C67)</f>
+        <f>B67-(2*C67)</f>
         <v>1.849</v>
       </c>
     </row>
@@ -2423,14 +2499,14 @@
         <v>130</v>
       </c>
       <c r="B69">
-        <v>30.83</v>
+        <v>32.69</v>
       </c>
       <c r="C69">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="D69">
         <f>B69-(1.5*C69)</f>
-        <v>28.474999999999998</v>
+        <v>29.164999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2459,7 +2535,7 @@
         <v>0.6633</v>
       </c>
       <c r="D71">
-        <f t="shared" si="2"/>
+        <f>B71-(2*C71)</f>
         <v>4.9234</v>
       </c>
     </row>
@@ -2654,7 +2730,7 @@
         <v>2.0099999999999998</v>
       </c>
       <c r="D84">
-        <f t="shared" ref="D84:D102" si="3">B84-(1.5*C84)</f>
+        <f t="shared" ref="D84:D102" si="2">B84-(1.5*C84)</f>
         <v>104.595</v>
       </c>
     </row>
@@ -2669,7 +2745,7 @@
         <v>3.18</v>
       </c>
       <c r="D85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>86.73</v>
       </c>
     </row>
@@ -2684,7 +2760,7 @@
         <v>1.97</v>
       </c>
       <c r="D86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>59.695</v>
       </c>
     </row>
@@ -2699,7 +2775,7 @@
         <v>16.64</v>
       </c>
       <c r="D87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>580.04</v>
       </c>
     </row>
@@ -2714,7 +2790,7 @@
         <v>4.13</v>
       </c>
       <c r="D88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>193.77500000000001</v>
       </c>
     </row>
@@ -2744,7 +2820,7 @@
         <v>0.63</v>
       </c>
       <c r="D90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>22.035</v>
       </c>
     </row>
@@ -2759,7 +2835,7 @@
         <v>1.01</v>
       </c>
       <c r="D91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>58.625</v>
       </c>
     </row>
@@ -2768,14 +2844,14 @@
         <v>194</v>
       </c>
       <c r="B92">
-        <v>20.6</v>
+        <v>13.39</v>
       </c>
       <c r="C92">
-        <v>0.71879999999999999</v>
+        <v>0.77280000000000004</v>
       </c>
       <c r="D92">
-        <f t="shared" si="3"/>
-        <v>19.521800000000002</v>
+        <f t="shared" si="2"/>
+        <v>12.2308</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2789,7 +2865,7 @@
         <v>0.73560000000000003</v>
       </c>
       <c r="D93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>10.8066</v>
       </c>
     </row>
@@ -2798,14 +2874,14 @@
         <v>198</v>
       </c>
       <c r="B94">
-        <v>11.98</v>
+        <v>10.8</v>
       </c>
       <c r="C94">
-        <v>0.86099999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="D94">
-        <f t="shared" si="3"/>
-        <v>10.688500000000001</v>
+        <f t="shared" si="2"/>
+        <v>9.1950000000000003</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2819,7 +2895,7 @@
         <v>5.05</v>
       </c>
       <c r="D95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>212.47500000000002</v>
       </c>
     </row>
@@ -2834,7 +2910,7 @@
         <v>0.45</v>
       </c>
       <c r="D96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>22.634999999999998</v>
       </c>
     </row>
@@ -2849,7 +2925,7 @@
         <v>0.45639999999999997</v>
       </c>
       <c r="D97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.9053999999999998</v>
       </c>
     </row>
@@ -2864,7 +2940,7 @@
         <v>7.54</v>
       </c>
       <c r="D98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>314.7</v>
       </c>
     </row>
@@ -2879,7 +2955,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="D99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>45.964999999999996</v>
       </c>
     </row>
@@ -2888,14 +2964,14 @@
         <v>212</v>
       </c>
       <c r="B100">
-        <v>75.900000000000006</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C100">
-        <v>1.33</v>
+        <v>2.11</v>
       </c>
       <c r="D100">
-        <f t="shared" si="3"/>
-        <v>73.905000000000001</v>
+        <f t="shared" si="2"/>
+        <v>74.625</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2909,7 +2985,7 @@
         <v>8.4599999999999995E-2</v>
       </c>
       <c r="D101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.3531</v>
       </c>
     </row>
@@ -2924,7 +3000,7 @@
         <v>2.71</v>
       </c>
       <c r="D102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>55.135000000000005</v>
       </c>
     </row>
@@ -2963,14 +3039,14 @@
         <v>246</v>
       </c>
       <c r="B105">
-        <v>8.2799999999999994</v>
+        <v>8.08</v>
       </c>
       <c r="C105">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="D105">
-        <f>B105-(1*C105)</f>
-        <v>7.9399999999999995</v>
+        <f>B105-(1.5*C105)</f>
+        <v>7.75</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -3029,7 +3105,7 @@
         <v>2.82</v>
       </c>
       <c r="D109">
-        <f>B109-(1.5*C109)</f>
+        <f t="shared" ref="D109:D121" si="3">B109-(1.5*C109)</f>
         <v>87.95</v>
       </c>
     </row>
@@ -3044,7 +3120,7 @@
         <v>0.9</v>
       </c>
       <c r="D110">
-        <f>B110-(1.5*C110)</f>
+        <f t="shared" si="3"/>
         <v>27.619999999999997</v>
       </c>
     </row>
@@ -3059,7 +3135,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="D111">
-        <f>B111-(1.5*C111)</f>
+        <f t="shared" si="3"/>
         <v>32.29</v>
       </c>
     </row>
@@ -3074,7 +3150,7 @@
         <v>2.08</v>
       </c>
       <c r="D112">
-        <f>B112-(1.5*C112)</f>
+        <f t="shared" si="3"/>
         <v>30.81</v>
       </c>
     </row>
@@ -3083,14 +3159,134 @@
         <v>266</v>
       </c>
       <c r="B113">
-        <v>181.5</v>
+        <v>177.01</v>
       </c>
       <c r="C113">
-        <v>7.21</v>
+        <v>6.77</v>
       </c>
       <c r="D113">
-        <f>B113-(1.5*C113)</f>
-        <v>170.685</v>
+        <f t="shared" si="3"/>
+        <v>166.85499999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>275</v>
+      </c>
+      <c r="B114">
+        <v>291.26</v>
+      </c>
+      <c r="C114">
+        <v>10.37</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="3"/>
+        <v>275.70499999999998</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>276</v>
+      </c>
+      <c r="B115">
+        <v>3.51</v>
+      </c>
+      <c r="C115">
+        <v>0.48209999999999997</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="3"/>
+        <v>2.7868499999999998</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>284</v>
+      </c>
+      <c r="B116">
+        <v>108.35</v>
+      </c>
+      <c r="C116">
+        <v>5.92</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="3"/>
+        <v>99.47</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>287</v>
+      </c>
+      <c r="B117">
+        <v>137.27000000000001</v>
+      </c>
+      <c r="C117">
+        <v>6.44</v>
+      </c>
+      <c r="D117">
+        <f t="shared" si="3"/>
+        <v>127.61000000000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>291</v>
+      </c>
+      <c r="B118">
+        <v>33.28</v>
+      </c>
+      <c r="C118">
+        <v>3.1</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="3"/>
+        <v>28.630000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>290</v>
+      </c>
+      <c r="B119">
+        <v>8.9</v>
+      </c>
+      <c r="C119">
+        <v>0.74280000000000002</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="3"/>
+        <v>7.7858000000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>292</v>
+      </c>
+      <c r="B120">
+        <v>20.69</v>
+      </c>
+      <c r="C120">
+        <v>1.81</v>
+      </c>
+      <c r="D120">
+        <f t="shared" si="3"/>
+        <v>17.975000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>293</v>
+      </c>
+      <c r="B121">
+        <v>67.819999999999993</v>
+      </c>
+      <c r="C121">
+        <v>6.21</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="3"/>
+        <v>58.504999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -3205,15 +3401,15 @@
       </c>
       <c r="B7">
         <f>VLOOKUP(A7,'Stop Loss Calculator'!$A$3:$D$99,2,FALSE)</f>
-        <v>2.95</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C7">
         <f>VLOOKUP(A7,'Stop Loss Calculator'!$A$3:$D$99,4,FALSE)</f>
-        <v>2.5960000000000001</v>
+        <v>3.9448000000000003</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>141.24293785310732</v>
+        <v>203.91517128874381</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3314,7 +3510,7 @@
         <v>4.2656000000000001</v>
       </c>
       <c r="D13">
-        <f t="shared" ref="D13" si="1">50/(B13-C13)</f>
+        <f>50/(B13-C13)</f>
         <v>159.03307888040712</v>
       </c>
     </row>
@@ -3325,7 +3521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2A77BB-0F93-4C87-9B0A-B8954405005E}">
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -3341,7 +3537,7 @@
       </c>
       <c r="B1" s="3">
         <f>COUNTIF(M:M,"Win")/COUNTA(M:M)</f>
-        <v>0.46226415094339623</v>
+        <v>0.47967479674796748</v>
       </c>
       <c r="C1" t="s">
         <v>92</v>
@@ -3353,7 +3549,7 @@
       </c>
       <c r="B2">
         <f>AVERAGEIF(M:M,"Win",I:I)</f>
-        <v>9.7235064318751352</v>
+        <v>9.1221741159303562</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -3362,7 +3558,7 @@
       </c>
       <c r="B3">
         <f>AVERAGEIF(M:M,"Loss",I:I)</f>
-        <v>-4.340372317043248</v>
+        <v>-4.3508279451477643</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -3371,7 +3567,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.3298109887618817</v>
+        <v>0.32979683123008535</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -3380,7 +3576,7 @@
       </c>
       <c r="B5">
         <f>(B1*B2+(1-B1)*B3)</f>
-        <v>2.1608546517963823</v>
+        <v>2.1118315800848304</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -3852,23 +4048,23 @@
         <v>118</v>
       </c>
       <c r="I18">
-        <f t="shared" ref="I18:I21" si="6">(E18-C18)/C18*(100)</f>
+        <f t="shared" ref="I18:I24" si="6">(E18-C18)/C18*(100)</f>
         <v>-8.9588377723970982</v>
       </c>
       <c r="J18">
-        <f t="shared" ref="J18:J20" si="7">(C18-F18)/C18*100</f>
+        <f t="shared" ref="J18:J24" si="7">(C18-F18)/C18*100</f>
         <v>8.8547215496368015</v>
       </c>
       <c r="K18">
-        <f t="shared" ref="K18:K20" si="8">(E18-C18)/C18*100</f>
+        <f t="shared" ref="K18:K24" si="8">(E18-C18)/C18*100</f>
         <v>-8.9588377723970982</v>
       </c>
       <c r="L18">
-        <f t="shared" ref="L18:L20" si="9">K18/J18</f>
+        <f t="shared" ref="L18:L24" si="9">K18/J18</f>
         <v>-1.0117582718074931</v>
       </c>
       <c r="M18" t="str">
-        <f t="shared" ref="M18:M20" si="10">IF(I18&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M18:M24" si="10">IF(I18&gt;0,"Win","Loss")</f>
         <v>Loss</v>
       </c>
       <c r="N18" t="s">
@@ -4000,19 +4196,19 @@
         <v>-2.5205392039562979</v>
       </c>
       <c r="J21">
-        <f t="shared" ref="J21" si="11">(C21-F21)/C21*100</f>
+        <f t="shared" si="7"/>
         <v>3.8884900693945923</v>
       </c>
       <c r="K21">
-        <f t="shared" ref="K21" si="12">(E21-C21)/C21*100</f>
+        <f t="shared" si="8"/>
         <v>-2.5205392039562979</v>
       </c>
       <c r="L21">
-        <f t="shared" ref="L21" si="13">K21/J21</f>
+        <f t="shared" si="9"/>
         <v>-0.64820512820513032</v>
       </c>
       <c r="M21" t="str">
-        <f t="shared" ref="M21" si="14">IF(I21&gt;0,"Win","Loss")</f>
+        <f t="shared" si="10"/>
         <v>Loss</v>
       </c>
       <c r="N21" t="s">
@@ -4044,23 +4240,23 @@
         <v>110</v>
       </c>
       <c r="I22">
-        <f t="shared" ref="I22" si="15">(E22-C22)/C22*(100)</f>
+        <f t="shared" si="6"/>
         <v>-5.5974165769644735</v>
       </c>
       <c r="J22">
-        <f t="shared" ref="J22" si="16">(C22-F22)/C22*100</f>
+        <f t="shared" si="7"/>
         <v>5.5882669537136689</v>
       </c>
       <c r="K22">
-        <f t="shared" ref="K22" si="17">(E22-C22)/C22*100</f>
+        <f t="shared" si="8"/>
         <v>-5.5974165769644735</v>
       </c>
       <c r="L22">
-        <f t="shared" ref="L22" si="18">K22/J22</f>
+        <f t="shared" si="9"/>
         <v>-1.0016372917268608</v>
       </c>
       <c r="M22" t="str">
-        <f t="shared" ref="M22" si="19">IF(I22&gt;0,"Win","Loss")</f>
+        <f t="shared" si="10"/>
         <v>Loss</v>
       </c>
       <c r="N22" t="s">
@@ -4092,23 +4288,23 @@
         <v>110</v>
       </c>
       <c r="I23">
-        <f t="shared" ref="I23:I24" si="20">(E23-C23)/C23*(100)</f>
+        <f t="shared" si="6"/>
         <v>6.4634349491920622</v>
       </c>
       <c r="J23">
-        <f t="shared" ref="J23:J24" si="21">(C23-F23)/C23*100</f>
+        <f t="shared" si="7"/>
         <v>4.1604197901049513</v>
       </c>
       <c r="K23">
-        <f t="shared" ref="K23:K24" si="22">(E23-C23)/C23*100</f>
+        <f t="shared" si="8"/>
         <v>6.4634349491920622</v>
       </c>
       <c r="L23">
-        <f t="shared" ref="L23:L24" si="23">K23/J23</f>
+        <f t="shared" si="9"/>
         <v>1.5535535535535501</v>
       </c>
       <c r="M23" t="str">
-        <f t="shared" ref="M23:M24" si="24">IF(I23&gt;0,"Win","Loss")</f>
+        <f t="shared" si="10"/>
         <v>Win</v>
       </c>
       <c r="N23" t="s">
@@ -4137,23 +4333,23 @@
         <v>25.200000000000003</v>
       </c>
       <c r="I24">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>-8.1936685288640696</v>
       </c>
       <c r="J24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>6.1452513966480389</v>
       </c>
       <c r="K24">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>-8.1936685288640696</v>
       </c>
       <c r="L24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="9"/>
         <v>-1.3333333333333361</v>
       </c>
       <c r="M24" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="10"/>
         <v>Loss</v>
       </c>
       <c r="N24" t="s">
@@ -4182,23 +4378,23 @@
         <v>57.52</v>
       </c>
       <c r="I25">
-        <f t="shared" ref="I25:I59" si="25">(E25-C25)/C25*(100)</f>
+        <f t="shared" ref="I25:I59" si="11">(E25-C25)/C25*(100)</f>
         <v>-8.8311688311688386</v>
       </c>
       <c r="J25">
-        <f t="shared" ref="J25:J59" si="26">(C25-F25)/C25*100</f>
+        <f t="shared" ref="J25:J59" si="12">(C25-F25)/C25*100</f>
         <v>6.62337662337662</v>
       </c>
       <c r="K25">
-        <f t="shared" ref="K25:K59" si="27">(E25-C25)/C25*100</f>
+        <f t="shared" ref="K25:K59" si="13">(E25-C25)/C25*100</f>
         <v>-8.8311688311688386</v>
       </c>
       <c r="L25">
-        <f t="shared" ref="L25:L59" si="28">K25/J25</f>
+        <f t="shared" ref="L25:L59" si="14">K25/J25</f>
         <v>-1.333333333333335</v>
       </c>
       <c r="M25" t="str">
-        <f t="shared" ref="M25:M59" si="29">IF(I25&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M25:M59" si="15">IF(I25&gt;0,"Win","Loss")</f>
         <v>Loss</v>
       </c>
       <c r="N25" t="s">
@@ -4230,23 +4426,23 @@
         <v>141</v>
       </c>
       <c r="I26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>7.4065685164212987</v>
       </c>
       <c r="J26">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>3.2616081540203803</v>
       </c>
       <c r="K26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>7.4065685164212987</v>
       </c>
       <c r="L26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>2.2708333333333388</v>
       </c>
       <c r="M26" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N26" t="s">
@@ -4278,23 +4474,23 @@
         <v>117</v>
       </c>
       <c r="I27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>14.288797755234201</v>
       </c>
       <c r="J27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>6.9933088711418137</v>
       </c>
       <c r="K27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>14.288797755234201</v>
       </c>
       <c r="L27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>2.0432098765432101</v>
       </c>
       <c r="M27" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N27" t="s">
@@ -4326,23 +4522,23 @@
         <v>117</v>
       </c>
       <c r="I28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>16.209799266134269</v>
       </c>
       <c r="J28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>6.9933088711418137</v>
       </c>
       <c r="K28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>16.209799266134269</v>
       </c>
       <c r="L28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>2.3179012345679015</v>
       </c>
       <c r="M28" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N28" t="s">
@@ -4374,23 +4570,23 @@
         <v>149</v>
       </c>
       <c r="I29">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>1.5310443677112477</v>
       </c>
       <c r="J29">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>2.0033878428562044</v>
       </c>
       <c r="K29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>1.5310443677112477</v>
       </c>
       <c r="L29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.76422764227642381</v>
       </c>
       <c r="M29" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N29" t="s">
@@ -4422,23 +4618,23 @@
         <v>152</v>
       </c>
       <c r="I30">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>2.7313800657174014</v>
       </c>
       <c r="J30">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>3.0188937568455616</v>
       </c>
       <c r="K30">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>2.7313800657174014</v>
       </c>
       <c r="L30">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.90476190476190099</v>
       </c>
       <c r="M30" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N30" t="s">
@@ -4457,36 +4653,36 @@
       </c>
       <c r="D31">
         <f>VLOOKUP(B31,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="E31">
         <v>7.47</v>
       </c>
       <c r="F31">
         <f t="shared" si="5"/>
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
       <c r="G31" t="s">
         <v>105</v>
       </c>
       <c r="I31">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-12.32394366197183</v>
       </c>
       <c r="J31">
-        <f t="shared" si="26"/>
-        <v>22.535211267605636</v>
+        <f t="shared" si="12"/>
+        <v>20.77464788732394</v>
       </c>
       <c r="K31">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-12.32394366197183</v>
       </c>
       <c r="L31">
-        <f t="shared" si="28"/>
-        <v>-0.54687499999999989</v>
+        <f t="shared" si="14"/>
+        <v>-0.59322033898305093</v>
       </c>
       <c r="M31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N31" t="s">
@@ -4518,23 +4714,23 @@
         <v>155</v>
       </c>
       <c r="I32">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>16.749406432117432</v>
       </c>
       <c r="J32">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>6.9933088711418137</v>
       </c>
       <c r="K32">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>16.749406432117432</v>
       </c>
       <c r="L32">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>2.3950617283950622</v>
       </c>
       <c r="M32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N32" t="s">
@@ -4566,23 +4762,23 @@
         <v>155</v>
       </c>
       <c r="I33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-1.8490374873353519</v>
       </c>
       <c r="J33">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>2.3936170212765968</v>
       </c>
       <c r="K33">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-1.8490374873353519</v>
       </c>
       <c r="L33">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-0.77248677248676889</v>
       </c>
       <c r="M33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N33" t="s">
@@ -4614,23 +4810,23 @@
         <v>105</v>
       </c>
       <c r="I34">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>1.8012422360248395</v>
       </c>
       <c r="J34">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>5.4037267080745286</v>
       </c>
       <c r="K34">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>1.8012422360248395</v>
       </c>
       <c r="L34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.3333333333333327</v>
       </c>
       <c r="M34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N34" t="s">
@@ -4662,23 +4858,23 @@
         <v>107</v>
       </c>
       <c r="I35">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>0.16637616859452384</v>
       </c>
       <c r="J35">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>3.2799873237204888</v>
       </c>
       <c r="K35">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>0.16637616859452384</v>
       </c>
       <c r="L35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>5.0724637681161339E-2</v>
       </c>
       <c r="M35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N35" t="s">
@@ -4710,23 +4906,23 @@
         <v>118</v>
       </c>
       <c r="I36">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>5.8142399605814221</v>
       </c>
       <c r="J36">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>6.6888396156688916</v>
       </c>
       <c r="K36">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>5.8142399605814221</v>
       </c>
       <c r="L36">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.86924493554327675</v>
       </c>
       <c r="M36" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N36" t="s">
@@ -4745,36 +4941,36 @@
       </c>
       <c r="D37">
         <f>VLOOKUP(B37,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>4.29</v>
+        <v>4.78</v>
       </c>
       <c r="E37">
         <v>91.73</v>
       </c>
       <c r="F37">
         <f t="shared" si="5"/>
-        <v>92.995000000000005</v>
+        <v>92.26</v>
       </c>
       <c r="G37" t="s">
         <v>162</v>
       </c>
       <c r="I37">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-7.7441416071608193</v>
       </c>
       <c r="J37">
-        <f t="shared" si="26"/>
-        <v>6.4718897716986845</v>
+        <f t="shared" si="12"/>
+        <v>7.2111032887458526</v>
       </c>
       <c r="K37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-7.7441416071608193</v>
       </c>
       <c r="L37">
-        <f t="shared" si="28"/>
-        <v>-1.1965811965811965</v>
+        <f t="shared" si="14"/>
+        <v>-1.073919107391911</v>
       </c>
       <c r="M37" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N37" t="s">
@@ -4793,36 +4989,36 @@
       </c>
       <c r="D38">
         <f>VLOOKUP(B38,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="E38">
         <v>14.06</v>
       </c>
       <c r="F38">
         <f t="shared" si="5"/>
-        <v>10.45</v>
+        <v>10.09</v>
       </c>
       <c r="G38" t="s">
         <v>164</v>
       </c>
       <c r="I38">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>17.069109075770196</v>
       </c>
       <c r="J38">
-        <f t="shared" si="26"/>
-        <v>12.989175686927565</v>
+        <f t="shared" si="12"/>
+        <v>15.986677768526228</v>
       </c>
       <c r="K38">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>17.069109075770196</v>
       </c>
       <c r="L38">
-        <f t="shared" si="28"/>
-        <v>1.3141025641025641</v>
+        <f t="shared" si="14"/>
+        <v>1.0677083333333337</v>
       </c>
       <c r="M38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N38" t="s">
@@ -4854,23 +5050,23 @@
         <v>164</v>
       </c>
       <c r="I39">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>1.7114695340501891</v>
       </c>
       <c r="J39">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>3.9516129032258034</v>
       </c>
       <c r="K39">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>1.7114695340501891</v>
       </c>
       <c r="L39">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.43310657596372165</v>
       </c>
       <c r="M39" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N39" t="s">
@@ -4902,23 +5098,23 @@
         <v>110</v>
       </c>
       <c r="I40">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-5.8056554166443055</v>
       </c>
       <c r="J40">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>4.3461930568224467</v>
       </c>
       <c r="K40">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-5.8056554166443055</v>
       </c>
       <c r="L40">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-1.3358024691358026</v>
       </c>
       <c r="M40" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N40" t="s">
@@ -4950,23 +5146,23 @@
         <v>110</v>
       </c>
       <c r="I41">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-5.6399132321041359</v>
       </c>
       <c r="J41">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>5.630694143167025</v>
       </c>
       <c r="K41">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-5.6399132321041359</v>
       </c>
       <c r="L41">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-1.0016372917268643</v>
       </c>
       <c r="M41" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N41" t="s">
@@ -4998,23 +5194,23 @@
         <v>155</v>
       </c>
       <c r="I42">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-5.2320291173794455</v>
       </c>
       <c r="J42">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>7.9845313921747003</v>
       </c>
       <c r="K42">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-5.2320291173794455</v>
       </c>
       <c r="L42">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-0.65527065527065675</v>
       </c>
       <c r="M42" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N42" t="s">
@@ -5046,23 +5242,23 @@
         <v>171</v>
       </c>
       <c r="I43">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-4.4685990338164157</v>
       </c>
       <c r="J43">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>4.0760869565217437</v>
       </c>
       <c r="K43">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-4.4685990338164157</v>
       </c>
       <c r="L43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-1.0962962962962928</v>
       </c>
       <c r="M43" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N43" t="s">
@@ -5094,23 +5290,23 @@
         <v>149</v>
       </c>
       <c r="I44">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>2.6695958990746229</v>
       </c>
       <c r="J44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>2.2168963451168446</v>
       </c>
       <c r="K44">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>2.6695958990746229</v>
       </c>
       <c r="L44">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>1.2042042042041972</v>
       </c>
       <c r="M44" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N44" t="s">
@@ -5142,23 +5338,23 @@
         <v>152</v>
       </c>
       <c r="I45">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-3.0911130499813084</v>
       </c>
       <c r="J45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>3.5148946778013128</v>
       </c>
       <c r="K45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-3.0911130499813084</v>
       </c>
       <c r="L45">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-0.87943262411347856</v>
       </c>
       <c r="M45" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N45" t="s">
@@ -5190,23 +5386,23 @@
         <v>149</v>
       </c>
       <c r="I46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>1.7414793953675505</v>
       </c>
       <c r="J46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>2.9829300534513465</v>
       </c>
       <c r="K46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>1.7414793953675505</v>
       </c>
       <c r="L46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.58381502890173453</v>
       </c>
       <c r="M46" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N46" t="s">
@@ -5225,36 +5421,36 @@
       </c>
       <c r="D47">
         <f>VLOOKUP(B47,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="E47">
         <v>13.75</v>
       </c>
       <c r="F47">
         <f t="shared" si="5"/>
-        <v>10.43</v>
+        <v>10.07</v>
       </c>
       <c r="G47" t="s">
         <v>155</v>
       </c>
       <c r="I47">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>14.678899082568805</v>
       </c>
       <c r="J47">
-        <f t="shared" si="26"/>
-        <v>13.010842368640537</v>
+        <f t="shared" si="12"/>
+        <v>16.013344453711426</v>
       </c>
       <c r="K47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>14.678899082568805</v>
       </c>
       <c r="L47">
-        <f t="shared" si="28"/>
-        <v>1.1282051282051277</v>
+        <f t="shared" si="14"/>
+        <v>0.91666666666666652</v>
       </c>
       <c r="M47" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N47" t="s">
@@ -5286,23 +5482,23 @@
         <v>149</v>
       </c>
       <c r="I48">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J48">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>6.1094224924012144</v>
       </c>
       <c r="K48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L48">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M48" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N48" t="s">
@@ -5334,23 +5530,23 @@
         <v>176</v>
       </c>
       <c r="I49">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-1.9973253957982811</v>
       </c>
       <c r="J49">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>3.9666105862559822</v>
       </c>
       <c r="K49">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-1.9973253957982811</v>
       </c>
       <c r="L49">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-0.50353452963567147</v>
       </c>
       <c r="M49" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N49" t="s">
@@ -5379,23 +5575,23 @@
         <v>101.47499999999999</v>
       </c>
       <c r="I50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>3.6271413532395504</v>
       </c>
       <c r="J50">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>2.8854435831180023</v>
       </c>
       <c r="K50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>3.6271413532395504</v>
       </c>
       <c r="L50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>1.2570480928689902</v>
       </c>
       <c r="M50" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N50" t="s">
@@ -5427,23 +5623,23 @@
         <v>110</v>
       </c>
       <c r="I51">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>2.6300294406280735</v>
       </c>
       <c r="J51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>7.2129538763493661</v>
       </c>
       <c r="K51">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>2.6300294406280735</v>
       </c>
       <c r="L51">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.36462585034013678</v>
       </c>
       <c r="M51" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N51" t="s">
@@ -5475,23 +5671,23 @@
         <v>105</v>
       </c>
       <c r="I52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-3.6809815950920144</v>
       </c>
       <c r="J52">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>3.6234662576687131</v>
       </c>
       <c r="K52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-3.6809815950920144</v>
       </c>
       <c r="L52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-1.0158730158730127</v>
       </c>
       <c r="M52" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N52" t="s">
@@ -5523,23 +5719,23 @@
         <v>162</v>
       </c>
       <c r="I53">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>3.2287822878228694</v>
       </c>
       <c r="J53">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>4.8892988929889292</v>
       </c>
       <c r="K53">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>3.2287822878228694</v>
       </c>
       <c r="L53">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0.66037735849056434</v>
       </c>
       <c r="M53" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N53" t="s">
@@ -5571,23 +5767,23 @@
         <v>149</v>
       </c>
       <c r="I54">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-6.5419538343725963</v>
       </c>
       <c r="J54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>4.1926485067279256</v>
       </c>
       <c r="K54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-6.5419538343725963</v>
       </c>
       <c r="L54">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-1.5603392041748194</v>
       </c>
       <c r="M54" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N54" t="s">
@@ -5619,23 +5815,23 @@
         <v>183</v>
       </c>
       <c r="I55">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-6.1403508771929731</v>
       </c>
       <c r="J55">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>9.5029239766081837</v>
       </c>
       <c r="K55">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-6.1403508771929731</v>
       </c>
       <c r="L55">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-0.64615384615384541</v>
       </c>
       <c r="M55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N55" t="s">
@@ -5667,23 +5863,23 @@
         <v>185</v>
       </c>
       <c r="I56">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-2.3931623931623878</v>
       </c>
       <c r="J56">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>7.5641025641025621</v>
       </c>
       <c r="K56">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-2.3931623931623878</v>
       </c>
       <c r="L56">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-0.31638418079095981</v>
       </c>
       <c r="M56" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N56" t="s">
@@ -5715,23 +5911,23 @@
         <v>149</v>
       </c>
       <c r="I57">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-1.5684015107867721</v>
       </c>
       <c r="J57">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>2.1317457269060958</v>
       </c>
       <c r="K57">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-1.5684015107867721</v>
       </c>
       <c r="L57">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-0.73573573573573803</v>
       </c>
       <c r="M57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N57" t="s">
@@ -5763,23 +5959,23 @@
         <v>188</v>
       </c>
       <c r="I58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>9.6680841011103258</v>
       </c>
       <c r="J58">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>6.5556343019135337</v>
       </c>
       <c r="K58">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>9.6680841011103258</v>
       </c>
       <c r="L58">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>1.4747747747747757</v>
       </c>
       <c r="M58" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Win</v>
       </c>
       <c r="N58" t="s">
@@ -5811,23 +6007,23 @@
         <v>164</v>
       </c>
       <c r="I59">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>-5.5927342256214114</v>
       </c>
       <c r="J59">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>4.708413001912044</v>
       </c>
       <c r="K59">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>-5.5927342256214114</v>
       </c>
       <c r="L59">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>-1.1878172588832485</v>
       </c>
       <c r="M59" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="15"/>
         <v>Loss</v>
       </c>
       <c r="N59" t="s">
@@ -5859,23 +6055,23 @@
         <v>108</v>
       </c>
       <c r="I60">
-        <f t="shared" ref="I60:I74" si="30">(E60-C60)/C60*(100)</f>
+        <f t="shared" ref="I60:I74" si="16">(E60-C60)/C60*(100)</f>
         <v>-3.359683794466402</v>
       </c>
       <c r="J60">
-        <f t="shared" ref="J60:J74" si="31">(C60-F60)/C60*100</f>
+        <f t="shared" ref="J60:J74" si="17">(C60-F60)/C60*100</f>
         <v>8.0039525691699662</v>
       </c>
       <c r="K60">
-        <f t="shared" ref="K60:K74" si="32">(E60-C60)/C60*100</f>
+        <f t="shared" ref="K60:K74" si="18">(E60-C60)/C60*100</f>
         <v>-3.359683794466402</v>
       </c>
       <c r="L60">
-        <f t="shared" ref="L60:L74" si="33">K60/J60</f>
+        <f t="shared" ref="L60:L74" si="19">K60/J60</f>
         <v>-0.41975308641975262</v>
       </c>
       <c r="M60" t="str">
-        <f t="shared" ref="M60:M74" si="34">IF(I60&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M60:M74" si="20">IF(I60&gt;0,"Win","Loss")</f>
         <v>Loss</v>
       </c>
       <c r="N60" t="s">
@@ -5907,11 +6103,11 @@
         <v>149</v>
       </c>
       <c r="I61">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>-2.815723445776416</v>
       </c>
       <c r="J61">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>2.801784220797324</v>
       </c>
       <c r="K61">
@@ -5919,11 +6115,11 @@
         <v>-2.815723445776416</v>
       </c>
       <c r="L61">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>-1.0049751243781098</v>
       </c>
       <c r="M61" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Loss</v>
       </c>
       <c r="N61" t="s">
@@ -5955,23 +6151,23 @@
         <v>118</v>
       </c>
       <c r="I62">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>-2.6446354212811194</v>
       </c>
       <c r="J62">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>3.3556303712235267</v>
       </c>
       <c r="K62">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>-2.6446354212811194</v>
       </c>
       <c r="L62">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>-0.78811881188118915</v>
       </c>
       <c r="M62" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Loss</v>
       </c>
       <c r="N62" t="s">
@@ -6003,23 +6199,23 @@
         <v>171</v>
       </c>
       <c r="I63">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>-6.1265316329082227</v>
       </c>
       <c r="J63">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>3.2883220805201243</v>
       </c>
       <c r="K63">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>-6.1265316329082227</v>
       </c>
       <c r="L63">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>-1.8631178707224354</v>
       </c>
       <c r="M63" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Loss</v>
       </c>
       <c r="N63" t="s">
@@ -6051,23 +6247,23 @@
         <v>162</v>
       </c>
       <c r="I64">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>3.0479605558045706</v>
       </c>
       <c r="J64">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>4.2357687135813551</v>
       </c>
       <c r="K64">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>3.0479605558045706</v>
       </c>
       <c r="L64">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>0.71957671957671898</v>
       </c>
       <c r="M64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Win</v>
       </c>
       <c r="N64" t="s">
@@ -6099,23 +6295,23 @@
         <v>164</v>
       </c>
       <c r="I65">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>-4.9363796786477181</v>
       </c>
       <c r="J65">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>5.9905266090833127</v>
       </c>
       <c r="K65">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>-4.9363796786477181</v>
       </c>
       <c r="L65">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>-0.82403100775193738</v>
       </c>
       <c r="M65" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Loss</v>
       </c>
       <c r="N65" t="s">
@@ -6134,36 +6330,36 @@
       </c>
       <c r="D66">
         <f>VLOOKUP(B66,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.71879999999999999</v>
+        <v>0.77280000000000004</v>
       </c>
       <c r="E66">
         <v>23.16</v>
       </c>
       <c r="F66">
         <f t="shared" si="5"/>
-        <v>19.6218</v>
+        <v>19.540800000000001</v>
       </c>
       <c r="G66" t="s">
         <v>176</v>
       </c>
       <c r="I66">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>11.884057971014498</v>
       </c>
       <c r="J66">
-        <f t="shared" si="31"/>
-        <v>5.2086956521739083</v>
+        <f t="shared" si="17"/>
+        <v>5.5999999999999925</v>
       </c>
       <c r="K66">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>11.884057971014498</v>
       </c>
       <c r="L66">
-        <f t="shared" si="33"/>
-        <v>2.2815804117974432</v>
+        <f t="shared" si="19"/>
+        <v>2.1221532091097344</v>
       </c>
       <c r="M66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Win</v>
       </c>
       <c r="N66" t="s">
@@ -6195,23 +6391,23 @@
         <v>152</v>
       </c>
       <c r="I67">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>-6.6453050989133473</v>
       </c>
       <c r="J67">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>5.9905266090833127</v>
       </c>
       <c r="K67">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>-6.6453050989133473</v>
       </c>
       <c r="L67">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>-1.109302325581395</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Loss</v>
       </c>
       <c r="N67" t="s">
@@ -6230,36 +6426,36 @@
       </c>
       <c r="D68">
         <f>VLOOKUP(B68,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.71879999999999999</v>
+        <v>0.77280000000000004</v>
       </c>
       <c r="E68">
         <v>18.559999999999999</v>
       </c>
       <c r="F68">
         <f t="shared" si="5"/>
-        <v>19.6218</v>
+        <v>19.540800000000001</v>
       </c>
       <c r="G68" t="s">
         <v>107</v>
       </c>
       <c r="I68">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>-10.338164251207733</v>
       </c>
       <c r="J68">
-        <f t="shared" si="31"/>
-        <v>5.2086956521739083</v>
+        <f t="shared" si="17"/>
+        <v>5.5999999999999925</v>
       </c>
       <c r="K68">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>-10.338164251207733</v>
       </c>
       <c r="L68">
-        <f t="shared" si="33"/>
-        <v>-1.9847894639213528</v>
+        <f t="shared" si="19"/>
+        <v>-1.8461007591442404</v>
       </c>
       <c r="M68" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Loss</v>
       </c>
       <c r="N68" t="s">
@@ -6291,23 +6487,23 @@
         <v>113</v>
       </c>
       <c r="I69">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>-4.6436285097192318</v>
       </c>
       <c r="J69">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>5.831533477321817</v>
       </c>
       <c r="K69">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>-4.6436285097192318</v>
       </c>
       <c r="L69">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>-0.7962962962962975</v>
       </c>
       <c r="M69" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Loss</v>
       </c>
       <c r="N69" t="s">
@@ -6339,23 +6535,23 @@
         <v>213</v>
       </c>
       <c r="I70">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>11.110497847444528</v>
       </c>
       <c r="J70">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>3.4192515730213007</v>
       </c>
       <c r="K70">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>11.110497847444528</v>
       </c>
       <c r="L70">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>3.24939467312349</v>
       </c>
       <c r="M70" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Win</v>
       </c>
       <c r="N70" t="s">
@@ -6374,36 +6570,36 @@
       </c>
       <c r="D71">
         <f>VLOOKUP(B71,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.86099999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="E71">
         <v>10.94</v>
       </c>
       <c r="F71">
         <f t="shared" si="5"/>
-        <v>8.0085000000000015</v>
+        <v>7.6950000000000003</v>
       </c>
       <c r="G71" t="s">
         <v>108</v>
       </c>
       <c r="I71">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>17.634408602150522</v>
       </c>
       <c r="J71">
-        <f t="shared" si="31"/>
-        <v>13.887096774193539</v>
+        <f t="shared" si="17"/>
+        <v>17.258064516129036</v>
       </c>
       <c r="K71">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>17.634408602150522</v>
       </c>
       <c r="L71">
-        <f t="shared" si="33"/>
-        <v>1.2698412698412695</v>
+        <f t="shared" si="19"/>
+        <v>1.0218068535825535</v>
       </c>
       <c r="M71" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Win</v>
       </c>
       <c r="N71" t="s">
@@ -6422,36 +6618,36 @@
       </c>
       <c r="D72">
         <f>VLOOKUP(B72,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.86099999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="E72">
         <v>11.75</v>
       </c>
       <c r="F72">
         <f t="shared" si="5"/>
-        <v>8.0085000000000015</v>
+        <v>7.6950000000000003</v>
       </c>
       <c r="G72" t="s">
         <v>149</v>
       </c>
       <c r="I72">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>26.344086021505365</v>
       </c>
       <c r="J72">
-        <f t="shared" si="31"/>
-        <v>13.887096774193539</v>
+        <f t="shared" si="17"/>
+        <v>17.258064516129036</v>
       </c>
       <c r="K72">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>26.344086021505365</v>
       </c>
       <c r="L72">
-        <f t="shared" si="33"/>
-        <v>1.8970189701897024</v>
+        <f t="shared" si="19"/>
+        <v>1.5264797507788153</v>
       </c>
       <c r="M72" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Win</v>
       </c>
       <c r="N72" t="s">
@@ -6483,23 +6679,23 @@
         <v>108</v>
       </c>
       <c r="I73">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>10.283159463487335</v>
       </c>
       <c r="J73">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>3.3532041728763078</v>
       </c>
       <c r="K73">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>10.283159463487335</v>
       </c>
       <c r="L73">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>3.0666666666666642</v>
       </c>
       <c r="M73" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Win</v>
       </c>
       <c r="N73" t="s">
@@ -6531,23 +6727,23 @@
         <v>108</v>
       </c>
       <c r="I74">
-        <f t="shared" si="30"/>
+        <f t="shared" si="16"/>
         <v>11.475409836065586</v>
       </c>
       <c r="J74">
-        <f t="shared" si="31"/>
+        <f t="shared" si="17"/>
         <v>3.3532041728763078</v>
       </c>
       <c r="K74">
-        <f t="shared" si="32"/>
+        <f t="shared" si="18"/>
         <v>11.475409836065586</v>
       </c>
       <c r="L74">
-        <f t="shared" si="33"/>
+        <f t="shared" si="19"/>
         <v>3.4222222222222221</v>
       </c>
       <c r="M74" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="20"/>
         <v>Win</v>
       </c>
       <c r="N74" t="s">
@@ -6579,23 +6775,23 @@
         <v>118</v>
       </c>
       <c r="I75">
-        <f t="shared" ref="I75:I92" si="35">(E75-C75)/C75*(100)</f>
+        <f t="shared" ref="I75:I92" si="21">(E75-C75)/C75*(100)</f>
         <v>-3.9735099337748379</v>
       </c>
       <c r="J75">
-        <f t="shared" ref="J75:J92" si="36">(C75-F75)/C75*100</f>
+        <f t="shared" ref="J75:J92" si="22">(C75-F75)/C75*100</f>
         <v>8.4039735099337758</v>
       </c>
       <c r="K75">
-        <f t="shared" ref="K75:K92" si="37">(E75-C75)/C75*100</f>
+        <f t="shared" ref="K75:K92" si="23">(E75-C75)/C75*100</f>
         <v>-3.9735099337748379</v>
       </c>
       <c r="L75">
-        <f t="shared" ref="L75:L92" si="38">K75/J75</f>
+        <f t="shared" ref="L75:L92" si="24">K75/J75</f>
         <v>-0.47281323877068593</v>
       </c>
       <c r="M75" t="str">
-        <f t="shared" ref="M75:M92" si="39">IF(I75&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M75:M92" si="25">IF(I75&gt;0,"Win","Loss")</f>
         <v>Loss</v>
       </c>
       <c r="N75" t="s">
@@ -6627,23 +6823,23 @@
         <v>183</v>
       </c>
       <c r="I76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>2.5203465476502851</v>
       </c>
       <c r="J76">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>2.4809661328432662</v>
       </c>
       <c r="K76">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>2.5203465476502851</v>
       </c>
       <c r="L76">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>1.0158730158730089</v>
       </c>
       <c r="M76" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N76" t="s">
@@ -6675,23 +6871,23 @@
         <v>113</v>
       </c>
       <c r="I77">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>30.075187969924805</v>
       </c>
       <c r="J77">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>11.560150375939852</v>
       </c>
       <c r="K77">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>30.075187969924805</v>
       </c>
       <c r="L77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>2.6016260162601617</v>
       </c>
       <c r="M77" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N77" t="s">
@@ -6710,36 +6906,36 @@
       </c>
       <c r="D78">
         <f>VLOOKUP(B78,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="E78">
         <v>36.22</v>
       </c>
       <c r="F78">
         <f t="shared" si="5"/>
-        <v>28.474999999999998</v>
+        <v>27.305</v>
       </c>
       <c r="G78" t="s">
         <v>108</v>
       </c>
       <c r="I78">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>17.482971132014274</v>
       </c>
       <c r="J78">
-        <f t="shared" si="36"/>
-        <v>7.6386636393123597</v>
+        <f t="shared" si="22"/>
+        <v>11.433668504703206</v>
       </c>
       <c r="K78">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>17.482971132014274</v>
       </c>
       <c r="L78">
-        <f t="shared" si="38"/>
-        <v>2.2887473460721868</v>
+        <f t="shared" si="24"/>
+        <v>1.529078014184398</v>
       </c>
       <c r="M78" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N78" t="s">
@@ -6771,23 +6967,23 @@
         <v>164</v>
       </c>
       <c r="I79">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>7.1211463308727767</v>
       </c>
       <c r="J79">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>4.1033434650455938</v>
       </c>
       <c r="K79">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>7.1211463308727767</v>
       </c>
       <c r="L79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>1.7354497354497356</v>
       </c>
       <c r="M79" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N79" t="s">
@@ -6806,36 +7002,36 @@
       </c>
       <c r="D80">
         <f>VLOOKUP(B80,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>4.29</v>
+        <v>4.78</v>
       </c>
       <c r="E80">
         <v>104.54</v>
       </c>
       <c r="F80">
         <f t="shared" si="5"/>
-        <v>100.41499999999999</v>
+        <v>99.679999999999993</v>
       </c>
       <c r="G80" t="s">
         <v>118</v>
       </c>
       <c r="I80">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>-2.1619092185306394</v>
       </c>
       <c r="J80">
-        <f t="shared" si="36"/>
-        <v>6.0224613944782428</v>
+        <f t="shared" si="22"/>
+        <v>6.7103416003743588</v>
       </c>
       <c r="K80">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>-2.1619092185306394</v>
       </c>
       <c r="L80">
-        <f t="shared" si="38"/>
-        <v>-0.35897435897435703</v>
+        <f t="shared" si="24"/>
+        <v>-0.32217573221757145</v>
       </c>
       <c r="M80" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Loss</v>
       </c>
       <c r="N80" t="s">
@@ -6854,36 +7050,36 @@
       </c>
       <c r="D81">
         <f>VLOOKUP(B81,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.86099999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="E81">
         <v>11.23</v>
       </c>
       <c r="F81">
         <f t="shared" si="5"/>
-        <v>8.0085000000000015</v>
+        <v>7.6950000000000003</v>
       </c>
       <c r="G81" t="s">
         <v>152</v>
       </c>
       <c r="I81">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>20.752688172043008</v>
       </c>
       <c r="J81">
-        <f t="shared" si="36"/>
-        <v>13.887096774193539</v>
+        <f t="shared" si="22"/>
+        <v>17.258064516129036</v>
       </c>
       <c r="K81">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>20.752688172043008</v>
       </c>
       <c r="L81">
-        <f t="shared" si="38"/>
-        <v>1.4943863724351538</v>
+        <f t="shared" si="24"/>
+        <v>1.2024922118380059</v>
       </c>
       <c r="M81" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N81" t="s">
@@ -6915,23 +7111,23 @@
         <v>176</v>
       </c>
       <c r="I82">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>22.147651006711413</v>
       </c>
       <c r="J82">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>8.5167785234899327</v>
       </c>
       <c r="K82">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>22.147651006711413</v>
       </c>
       <c r="L82">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>2.6004728132387713</v>
       </c>
       <c r="M82" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N82" t="s">
@@ -6963,23 +7159,23 @@
         <v>227</v>
       </c>
       <c r="I83">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>0.46948356807511077</v>
       </c>
       <c r="J83">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>1.977619139494494</v>
       </c>
       <c r="K83">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>0.46948356807511077</v>
       </c>
       <c r="L83">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>0.23739837398373737</v>
       </c>
       <c r="M83" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N83" t="s">
@@ -6998,36 +7194,36 @@
       </c>
       <c r="D84">
         <f>VLOOKUP(B84,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="E84">
         <v>33.24</v>
       </c>
       <c r="F84">
         <f t="shared" si="5"/>
-        <v>28.474999999999998</v>
+        <v>27.305</v>
       </c>
       <c r="G84" t="s">
         <v>188</v>
       </c>
       <c r="I84">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>7.8170613039247607</v>
       </c>
       <c r="J84">
-        <f t="shared" si="36"/>
-        <v>7.6386636393123597</v>
+        <f t="shared" si="22"/>
+        <v>11.433668504703206</v>
       </c>
       <c r="K84">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>7.8170613039247607</v>
       </c>
       <c r="L84">
-        <f t="shared" si="38"/>
-        <v>1.02335456475584</v>
+        <f t="shared" si="24"/>
+        <v>0.68368794326241267</v>
       </c>
       <c r="M84" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N84" t="s">
@@ -7059,23 +7255,23 @@
         <v>105</v>
       </c>
       <c r="I85">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>8.7248322147651081</v>
       </c>
       <c r="J85">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>8.5167785234899327</v>
       </c>
       <c r="K85">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>8.7248322147651081</v>
       </c>
       <c r="L85">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>1.0244286840031529</v>
       </c>
       <c r="M85" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N85" t="s">
@@ -7107,23 +7303,23 @@
         <v>152</v>
       </c>
       <c r="I86">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>-4.0679387712308612</v>
       </c>
       <c r="J86">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>3.617110505347036</v>
       </c>
       <c r="K86">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>-4.0679387712308612</v>
       </c>
       <c r="L86">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>-1.1246376811594181</v>
       </c>
       <c r="M86" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Loss</v>
       </c>
       <c r="N86" t="s">
@@ -7155,23 +7351,23 @@
         <v>227</v>
       </c>
       <c r="I87">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>0.77175381053443215</v>
       </c>
       <c r="J87">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>1.977619139494494</v>
       </c>
       <c r="K87">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>0.77175381053443215</v>
       </c>
       <c r="L87">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>0.39024390243902213</v>
       </c>
       <c r="M87" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N87" t="s">
@@ -7203,23 +7399,23 @@
         <v>233</v>
       </c>
       <c r="I88">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>20.268256333830116</v>
       </c>
       <c r="J88">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>3.3532041728763078</v>
       </c>
       <c r="K88">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>20.268256333830116</v>
       </c>
       <c r="L88">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>6.0444444444444416</v>
       </c>
       <c r="M88" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N88" t="s">
@@ -7244,30 +7440,30 @@
         <v>327.12</v>
       </c>
       <c r="F89">
-        <f t="shared" ref="F89:F114" si="40">C89-(1.5*D89)</f>
+        <f t="shared" ref="F89:F131" si="26">C89-(1.5*D89)</f>
         <v>314.98500000000001</v>
       </c>
       <c r="G89" t="s">
         <v>118</v>
       </c>
       <c r="I89">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>-2.1711824869908458</v>
       </c>
       <c r="J89">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>5.8002870985106707</v>
       </c>
       <c r="K89">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>-2.1711824869908458</v>
       </c>
       <c r="L89">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>-0.37432327919566888</v>
       </c>
       <c r="M89" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Loss</v>
       </c>
       <c r="N89" t="s">
@@ -7292,30 +7488,30 @@
         <v>82.32</v>
       </c>
       <c r="F90">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>80.809999999999988</v>
       </c>
       <c r="G90" t="s">
         <v>105</v>
       </c>
       <c r="I90">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>0.26796589524969411</v>
       </c>
       <c r="J90">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>1.5712545676004948</v>
       </c>
       <c r="K90">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>0.26796589524969411</v>
       </c>
       <c r="L90">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>0.17054263565891303</v>
       </c>
       <c r="M90" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Win</v>
       </c>
       <c r="N90" t="s">
@@ -7340,30 +7536,30 @@
         <v>217.01</v>
       </c>
       <c r="F91">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>212.47500000000002</v>
       </c>
       <c r="G91" t="s">
         <v>113</v>
       </c>
       <c r="I91">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>-1.3815042035901024</v>
       </c>
       <c r="J91">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>3.4423994546693879</v>
       </c>
       <c r="K91">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>-1.3815042035901024</v>
       </c>
       <c r="L91">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>-0.40132013201320466</v>
       </c>
       <c r="M91" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Loss</v>
       </c>
       <c r="N91" t="s">
@@ -7388,30 +7584,30 @@
         <v>439.59</v>
       </c>
       <c r="F92">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>438.61</v>
       </c>
       <c r="G92" t="s">
         <v>118</v>
       </c>
       <c r="I92">
-        <f t="shared" si="35"/>
+        <f t="shared" si="21"/>
         <v>-4.8650637349319412</v>
       </c>
       <c r="J92">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
         <v>5.0771528123444458</v>
       </c>
       <c r="K92">
-        <f t="shared" si="37"/>
+        <f t="shared" si="23"/>
         <v>-4.8650637349319412</v>
       </c>
       <c r="L92">
-        <f t="shared" si="38"/>
+        <f t="shared" si="24"/>
         <v>-0.9582267689684586</v>
       </c>
       <c r="M92" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="25"/>
         <v>Loss</v>
       </c>
       <c r="N92" t="s">
@@ -7436,30 +7632,30 @@
         <v>189.01</v>
       </c>
       <c r="F93">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>182.66500000000002</v>
       </c>
       <c r="G93" t="s">
         <v>118</v>
       </c>
       <c r="I93">
-        <f t="shared" ref="I93:I114" si="41">(E93-C93)/C93*(100)</f>
+        <f t="shared" ref="I93:I116" si="27">(E93-C93)/C93*(100)</f>
         <v>-0.69353228602953898</v>
       </c>
       <c r="J93">
-        <f t="shared" ref="J93:J114" si="42">(C93-F93)/C93*100</f>
+        <f t="shared" ref="J93:J116" si="28">(C93-F93)/C93*100</f>
         <v>4.0272158881941849</v>
       </c>
       <c r="K93">
-        <f t="shared" ref="K93:K114" si="43">(E93-C93)/C93*100</f>
+        <f t="shared" ref="K93:K116" si="29">(E93-C93)/C93*100</f>
         <v>-0.69353228602953898</v>
       </c>
       <c r="L93">
-        <f t="shared" ref="L93:L114" si="44">K93/J93</f>
+        <f t="shared" ref="L93:L116" si="30">K93/J93</f>
         <v>-0.17221135029354506</v>
       </c>
       <c r="M93" t="str">
-        <f t="shared" ref="M93:M114" si="45">IF(I93&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M93:M116" si="31">IF(I93&gt;0,"Win","Loss")</f>
         <v>Loss</v>
       </c>
       <c r="N93" t="s">
@@ -7484,30 +7680,30 @@
         <v>324.79000000000002</v>
       </c>
       <c r="F94">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>313.41500000000002</v>
       </c>
       <c r="G94" t="s">
         <v>118</v>
       </c>
       <c r="I94">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-2.4097833598749983</v>
       </c>
       <c r="J94">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>5.8276494095730245</v>
       </c>
       <c r="K94">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-2.4097833598749983</v>
       </c>
       <c r="L94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.41350863624645467</v>
       </c>
       <c r="M94" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N94" t="s">
@@ -7532,30 +7728,30 @@
         <v>55.04</v>
       </c>
       <c r="F95">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>55.135000000000005</v>
       </c>
       <c r="G95" t="s">
         <v>176</v>
       </c>
       <c r="I95">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-7.0270270270270334</v>
       </c>
       <c r="J95">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>6.8665540540540499</v>
       </c>
       <c r="K95">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-7.0270270270270334</v>
       </c>
       <c r="L95">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-1.0233702337023385</v>
       </c>
       <c r="M95" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N95" t="s">
@@ -7580,30 +7776,30 @@
         <v>23.4</v>
       </c>
       <c r="F96">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>19.454999999999998</v>
       </c>
       <c r="G96" t="s">
         <v>244</v>
       </c>
       <c r="I96">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>16.24441132637854</v>
       </c>
       <c r="J96">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>3.3532041728763078</v>
       </c>
       <c r="K96">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>16.24441132637854</v>
       </c>
       <c r="L96">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>4.8444444444444388</v>
       </c>
       <c r="M96" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Win</v>
       </c>
       <c r="N96" t="s">
@@ -7622,36 +7818,36 @@
       </c>
       <c r="D97">
         <f>VLOOKUP(B97,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="E97">
         <v>8.73</v>
       </c>
       <c r="F97">
-        <f t="shared" si="40"/>
-        <v>7.46</v>
+        <f t="shared" si="26"/>
+        <v>7.64</v>
       </c>
       <c r="G97" t="s">
         <v>113</v>
       </c>
       <c r="I97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>9.5357590966123045</v>
       </c>
       <c r="J97">
-        <f t="shared" si="42"/>
-        <v>6.3989962358845647</v>
+        <f t="shared" si="28"/>
+        <v>4.1405269761606034</v>
       </c>
       <c r="K97">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>9.5357590966123045</v>
       </c>
       <c r="L97">
-        <f t="shared" si="44"/>
-        <v>1.4901960784313744</v>
+        <f t="shared" si="30"/>
+        <v>2.3030303030303045</v>
       </c>
       <c r="M97" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Win</v>
       </c>
       <c r="N97" t="s">
@@ -7676,30 +7872,30 @@
         <v>184.07</v>
       </c>
       <c r="F98">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>184.095</v>
       </c>
       <c r="G98" t="s">
         <v>176</v>
       </c>
       <c r="I98">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-4.010221109720483</v>
       </c>
       <c r="J98">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>3.9971839799749649</v>
       </c>
       <c r="K98">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-4.010221109720483</v>
       </c>
       <c r="L98">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-1.0032615786040451</v>
       </c>
       <c r="M98" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N98" t="s">
@@ -7724,30 +7920,30 @@
         <v>327.33</v>
       </c>
       <c r="F99">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>314.41500000000002</v>
       </c>
       <c r="G99" t="s">
         <v>113</v>
       </c>
       <c r="I99">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-1.9412240496090645</v>
       </c>
       <c r="J99">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>5.8101914262604426</v>
       </c>
       <c r="K99">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-1.9412240496090645</v>
       </c>
       <c r="L99">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.33410672853828427</v>
       </c>
       <c r="M99" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N99" t="s">
@@ -7772,30 +7968,30 @@
         <v>5.57</v>
       </c>
       <c r="F100">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>4.7050000000000001</v>
       </c>
       <c r="G100" t="s">
         <v>188</v>
       </c>
       <c r="I100">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>4.6992481203007515</v>
       </c>
       <c r="J100">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>11.560150375939852</v>
       </c>
       <c r="K100">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>4.6992481203007515</v>
       </c>
       <c r="L100">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>0.40650406504065029</v>
       </c>
       <c r="M100" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Win</v>
       </c>
       <c r="N100" t="s">
@@ -7820,30 +8016,30 @@
         <v>54.99</v>
       </c>
       <c r="F101">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>52.82</v>
       </c>
       <c r="G101" t="s">
         <v>176</v>
       </c>
       <c r="I101">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-1.9086692829111671</v>
       </c>
       <c r="J101">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>5.7795219407777418</v>
       </c>
       <c r="K101">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-1.9086692829111671</v>
       </c>
       <c r="L101">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.33024691358024677</v>
       </c>
       <c r="M101" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N101" t="s">
@@ -7862,36 +8058,36 @@
       </c>
       <c r="D102">
         <f>VLOOKUP(B102,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="E102">
         <v>8.2200000000000006</v>
       </c>
       <c r="F102">
-        <f t="shared" si="40"/>
-        <v>7.46</v>
+        <f t="shared" si="26"/>
+        <v>7.64</v>
       </c>
       <c r="G102" t="s">
         <v>107</v>
       </c>
       <c r="I102">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>3.1367628607277402</v>
       </c>
       <c r="J102">
-        <f t="shared" si="42"/>
-        <v>6.3989962358845647</v>
+        <f t="shared" si="28"/>
+        <v>4.1405269761606034</v>
       </c>
       <c r="K102">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>3.1367628607277402</v>
       </c>
       <c r="L102">
-        <f t="shared" si="44"/>
-        <v>0.49019607843137447</v>
+        <f t="shared" si="30"/>
+        <v>0.75757575757576012</v>
       </c>
       <c r="M102" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Win</v>
       </c>
       <c r="N102" t="s">
@@ -7916,30 +8112,30 @@
         <v>311.27999999999997</v>
       </c>
       <c r="F103">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>314.7</v>
       </c>
       <c r="G103" t="s">
         <v>105</v>
       </c>
       <c r="I103">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-4.5182663108493664</v>
       </c>
       <c r="J103">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>3.4692187356216078</v>
       </c>
       <c r="K103">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-4.5182663108493664</v>
       </c>
       <c r="L103">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-1.3023872679045105</v>
       </c>
       <c r="M103" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N103" t="s">
@@ -7964,30 +8160,30 @@
         <v>56.05</v>
       </c>
       <c r="F104">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>54.96</v>
       </c>
       <c r="G104" t="s">
         <v>113</v>
       </c>
       <c r="I104">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-2.5386889236654513</v>
       </c>
       <c r="J104">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>4.4340114762649927</v>
       </c>
       <c r="K104">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-2.5386889236654513</v>
       </c>
       <c r="L104">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.5725490196078441</v>
       </c>
       <c r="M104" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N104" t="s">
@@ -8012,30 +8208,30 @@
         <v>538</v>
       </c>
       <c r="F105">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>525.49</v>
       </c>
       <c r="G105" t="s">
         <v>105</v>
       </c>
       <c r="I105">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-0.74716354579834976</v>
       </c>
       <c r="J105">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>3.0550687205977209</v>
       </c>
       <c r="K105">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-0.74716354579834976</v>
       </c>
       <c r="L105">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.24456521739130241</v>
       </c>
       <c r="M105" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N105" t="s">
@@ -8060,30 +8256,30 @@
         <v>27.84</v>
       </c>
       <c r="F106">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>27.61</v>
       </c>
       <c r="G106" t="s">
         <v>118</v>
       </c>
       <c r="I106">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-3.8674033149171305</v>
       </c>
       <c r="J106">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>4.661602209944756</v>
       </c>
       <c r="K106">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-3.8674033149171305</v>
       </c>
       <c r="L106">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.82962962962962949</v>
       </c>
       <c r="M106" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N106" t="s">
@@ -8108,30 +8304,30 @@
         <v>193.53</v>
       </c>
       <c r="F107">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>174.88500000000002</v>
       </c>
       <c r="G107" t="s">
         <v>261</v>
       </c>
       <c r="I107">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>6.875414181577197</v>
       </c>
       <c r="J107">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>3.4211398277004599</v>
       </c>
       <c r="K107">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>6.875414181577197</v>
       </c>
       <c r="L107">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>2.0096852300242136</v>
       </c>
       <c r="M107" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Win</v>
       </c>
       <c r="N107" t="s">
@@ -8156,30 +8352,30 @@
         <v>55.66</v>
       </c>
       <c r="F108">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>55.72</v>
       </c>
       <c r="G108" t="s">
         <v>176</v>
       </c>
       <c r="I108">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-5.5970149253731414</v>
       </c>
       <c r="J108">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>5.495251017639081</v>
       </c>
       <c r="K108">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-5.5970149253731414</v>
       </c>
       <c r="L108">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-1.018518518518519</v>
       </c>
       <c r="M108" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N108" t="s">
@@ -8198,36 +8394,36 @@
       </c>
       <c r="D109">
         <f>VLOOKUP(B109,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="E109">
         <v>9.39</v>
       </c>
       <c r="F109">
-        <f t="shared" si="40"/>
-        <v>8.16</v>
+        <f t="shared" si="26"/>
+        <v>8.31</v>
       </c>
       <c r="G109" t="s">
         <v>113</v>
       </c>
       <c r="I109">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-6.8452380952380905</v>
       </c>
       <c r="J109">
-        <f t="shared" si="42"/>
-        <v>19.047619047619047</v>
+        <f t="shared" si="28"/>
+        <v>17.559523809523807</v>
       </c>
       <c r="K109">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-6.8452380952380905</v>
       </c>
       <c r="L109">
-        <f t="shared" si="44"/>
-        <v>-0.35937499999999978</v>
+        <f t="shared" si="30"/>
+        <v>-0.38983050847457607</v>
       </c>
       <c r="M109" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N109" t="s">
@@ -8252,30 +8448,30 @@
         <v>63.83</v>
       </c>
       <c r="F110">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>55.970000000000006</v>
       </c>
       <c r="G110" t="s">
         <v>176</v>
       </c>
       <c r="I110">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>9.07382091592617</v>
       </c>
       <c r="J110">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>4.3574846206425102</v>
       </c>
       <c r="K110">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>9.07382091592617</v>
       </c>
       <c r="L110">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>2.0823529411764712</v>
       </c>
       <c r="M110" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Win</v>
       </c>
       <c r="N110" t="s">
@@ -8300,30 +8496,30 @@
         <v>11.29</v>
       </c>
       <c r="F111">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>10.38</v>
       </c>
       <c r="G111" t="s">
         <v>113</v>
       </c>
       <c r="I111">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-3.0068728522336894</v>
       </c>
       <c r="J111">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>10.824742268041234</v>
       </c>
       <c r="K111">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-3.0068728522336894</v>
       </c>
       <c r="L111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.27777777777777901</v>
       </c>
       <c r="M111" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N111" t="s">
@@ -8348,30 +8544,30 @@
         <v>31.3</v>
       </c>
       <c r="F112">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>30.81</v>
       </c>
       <c r="G112" t="s">
         <v>176</v>
       </c>
       <c r="I112">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-7.7512525788387823</v>
       </c>
       <c r="J112">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>9.1954022988505777</v>
       </c>
       <c r="K112">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-7.7512525788387823</v>
       </c>
       <c r="L112">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.84294871794871729</v>
       </c>
       <c r="M112" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N112" t="s">
@@ -8396,30 +8592,30 @@
         <v>88.63</v>
       </c>
       <c r="F113">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>87.95</v>
       </c>
       <c r="G113" t="s">
         <v>271</v>
       </c>
       <c r="I113">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-3.8511607724018351</v>
       </c>
       <c r="J113">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>4.5888479062703453</v>
       </c>
       <c r="K113">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-3.8511607724018351</v>
       </c>
       <c r="L113">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.83924349881796878</v>
       </c>
       <c r="M113" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N113" t="s">
@@ -8444,39 +8640,855 @@
         <v>52.94</v>
       </c>
       <c r="F114">
-        <f t="shared" si="40"/>
+        <f t="shared" si="26"/>
         <v>52.54</v>
       </c>
       <c r="G114" t="s">
         <v>271</v>
       </c>
       <c r="I114">
-        <f t="shared" si="41"/>
+        <f t="shared" si="27"/>
         <v>-2.0898834843721148</v>
       </c>
       <c r="J114">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>2.8296652487516205</v>
       </c>
       <c r="K114">
-        <f t="shared" si="43"/>
+        <f t="shared" si="29"/>
         <v>-2.0898834843721148</v>
       </c>
       <c r="L114">
-        <f t="shared" si="44"/>
+        <f t="shared" si="30"/>
         <v>-0.73856209150326901</v>
       </c>
       <c r="M114" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="31"/>
         <v>Loss</v>
       </c>
       <c r="N114" t="s">
         <v>273</v>
       </c>
     </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>46070</v>
+      </c>
+      <c r="B115" t="s">
+        <v>123</v>
+      </c>
+      <c r="C115">
+        <v>10.31</v>
+      </c>
+      <c r="D115">
+        <f>VLOOKUP(B115,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.91759999999999997</v>
+      </c>
+      <c r="E115">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="F115">
+        <f t="shared" si="26"/>
+        <v>8.9336000000000002</v>
+      </c>
+      <c r="G115" t="s">
+        <v>118</v>
+      </c>
+      <c r="I115">
+        <f t="shared" si="27"/>
+        <v>-4.170708050436466</v>
+      </c>
+      <c r="J115">
+        <f t="shared" si="28"/>
+        <v>13.350145489815715</v>
+      </c>
+      <c r="K115">
+        <f t="shared" si="29"/>
+        <v>-4.170708050436466</v>
+      </c>
+      <c r="L115">
+        <f t="shared" si="30"/>
+        <v>-0.31240918337692503</v>
+      </c>
+      <c r="M115" t="str">
+        <f t="shared" si="31"/>
+        <v>Loss</v>
+      </c>
+      <c r="N115" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>46071</v>
+      </c>
+      <c r="B116" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116">
+        <v>40.99</v>
+      </c>
+      <c r="D116">
+        <f>VLOOKUP(B116,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.63</v>
+      </c>
+      <c r="E116">
+        <v>42.04</v>
+      </c>
+      <c r="F116">
+        <f t="shared" si="26"/>
+        <v>40.045000000000002</v>
+      </c>
+      <c r="G116" t="s">
+        <v>105</v>
+      </c>
+      <c r="I116">
+        <f t="shared" si="27"/>
+        <v>2.5616003903391</v>
+      </c>
+      <c r="J116">
+        <f t="shared" si="28"/>
+        <v>2.3054403513051969</v>
+      </c>
+      <c r="K116">
+        <f t="shared" si="29"/>
+        <v>2.5616003903391</v>
+      </c>
+      <c r="L116">
+        <f t="shared" si="30"/>
+        <v>1.1111111111111078</v>
+      </c>
+      <c r="M116" t="str">
+        <f t="shared" si="31"/>
+        <v>Win</v>
+      </c>
+      <c r="N116" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>46071</v>
+      </c>
+      <c r="B117" t="s">
+        <v>145</v>
+      </c>
+      <c r="C117">
+        <v>36.229999999999997</v>
+      </c>
+      <c r="D117">
+        <f>VLOOKUP(B117,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.06</v>
+      </c>
+      <c r="E117">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F117">
+        <f t="shared" si="26"/>
+        <v>34.639999999999993</v>
+      </c>
+      <c r="G117" t="s">
+        <v>171</v>
+      </c>
+      <c r="I117">
+        <f t="shared" ref="I117:I131" si="32">(E117-C117)/C117*(100)</f>
+        <v>1.2972674579078278</v>
+      </c>
+      <c r="J117">
+        <f t="shared" ref="J117:J131" si="33">(C117-F117)/C117*100</f>
+        <v>4.3886282086668604</v>
+      </c>
+      <c r="K117">
+        <f t="shared" ref="K117:K131" si="34">(E117-C117)/C117*100</f>
+        <v>1.2972674579078278</v>
+      </c>
+      <c r="L117">
+        <f t="shared" ref="L117:L131" si="35">K117/J117</f>
+        <v>0.29559748427673271</v>
+      </c>
+      <c r="M117" t="str">
+        <f t="shared" ref="M117:M131" si="36">IF(I117&gt;0,"Win","Loss")</f>
+        <v>Win</v>
+      </c>
+      <c r="N117" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>46072</v>
+      </c>
+      <c r="B118" t="s">
+        <v>251</v>
+      </c>
+      <c r="C118">
+        <v>19.23</v>
+      </c>
+      <c r="D118">
+        <f>VLOOKUP(B118,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.4</v>
+      </c>
+      <c r="E118">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="F118">
+        <f t="shared" si="26"/>
+        <v>18.63</v>
+      </c>
+      <c r="G118" t="s">
+        <v>108</v>
+      </c>
+      <c r="I118">
+        <f t="shared" si="32"/>
+        <v>0.62402496099844507</v>
+      </c>
+      <c r="J118">
+        <f t="shared" si="33"/>
+        <v>3.1201248049922072</v>
+      </c>
+      <c r="K118">
+        <f t="shared" si="34"/>
+        <v>0.62402496099844507</v>
+      </c>
+      <c r="L118">
+        <f t="shared" si="35"/>
+        <v>0.20000000000000115</v>
+      </c>
+      <c r="M118" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N118" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>46072</v>
+      </c>
+      <c r="B119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C119">
+        <v>27.83</v>
+      </c>
+      <c r="D119">
+        <f>VLOOKUP(B119,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.63</v>
+      </c>
+      <c r="E119">
+        <v>26.95</v>
+      </c>
+      <c r="F119">
+        <f t="shared" si="26"/>
+        <v>26.884999999999998</v>
+      </c>
+      <c r="G119" t="s">
+        <v>107</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="32"/>
+        <v>-3.1620553359683758</v>
+      </c>
+      <c r="J119">
+        <f t="shared" si="33"/>
+        <v>3.3956162414660449</v>
+      </c>
+      <c r="K119">
+        <f t="shared" si="34"/>
+        <v>-3.1620553359683758</v>
+      </c>
+      <c r="L119">
+        <f t="shared" si="35"/>
+        <v>-0.93121693121692983</v>
+      </c>
+      <c r="M119" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N119" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>46072</v>
+      </c>
+      <c r="B120" t="s">
+        <v>19</v>
+      </c>
+      <c r="C120">
+        <v>40.99</v>
+      </c>
+      <c r="D120">
+        <f>VLOOKUP(B120,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.63</v>
+      </c>
+      <c r="E120">
+        <v>42.45</v>
+      </c>
+      <c r="F120">
+        <f t="shared" si="26"/>
+        <v>40.045000000000002</v>
+      </c>
+      <c r="G120" t="s">
+        <v>280</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="32"/>
+        <v>3.5618443522810459</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="33"/>
+        <v>2.3054403513051969</v>
+      </c>
+      <c r="K120">
+        <f t="shared" si="34"/>
+        <v>3.5618443522810459</v>
+      </c>
+      <c r="L120">
+        <f t="shared" si="35"/>
+        <v>1.5449735449735453</v>
+      </c>
+      <c r="M120" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N120" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>46072</v>
+      </c>
+      <c r="B121" t="s">
+        <v>145</v>
+      </c>
+      <c r="C121">
+        <v>36.229999999999997</v>
+      </c>
+      <c r="D121">
+        <f>VLOOKUP(B121,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.06</v>
+      </c>
+      <c r="E121">
+        <v>35.82</v>
+      </c>
+      <c r="F121">
+        <f t="shared" si="26"/>
+        <v>34.639999999999993</v>
+      </c>
+      <c r="G121" t="s">
+        <v>271</v>
+      </c>
+      <c r="I121">
+        <f t="shared" si="32"/>
+        <v>-1.1316588462599964</v>
+      </c>
+      <c r="J121">
+        <f t="shared" si="33"/>
+        <v>4.3886282086668604</v>
+      </c>
+      <c r="K121">
+        <f t="shared" si="34"/>
+        <v>-1.1316588462599964</v>
+      </c>
+      <c r="L121">
+        <f t="shared" si="35"/>
+        <v>-0.25786163522012312</v>
+      </c>
+      <c r="M121" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N121" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>46076</v>
+      </c>
+      <c r="B122" t="s">
+        <v>275</v>
+      </c>
+      <c r="C122">
+        <v>291.26</v>
+      </c>
+      <c r="D122">
+        <f>VLOOKUP(B122,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>10.37</v>
+      </c>
+      <c r="E122">
+        <v>287.49</v>
+      </c>
+      <c r="F122">
+        <f t="shared" si="26"/>
+        <v>275.70499999999998</v>
+      </c>
+      <c r="G122" t="s">
+        <v>105</v>
+      </c>
+      <c r="I122">
+        <f t="shared" si="32"/>
+        <v>-1.2943761587584912</v>
+      </c>
+      <c r="J122">
+        <f t="shared" si="33"/>
+        <v>5.3405891643205408</v>
+      </c>
+      <c r="K122">
+        <f t="shared" si="34"/>
+        <v>-1.2943761587584912</v>
+      </c>
+      <c r="L122">
+        <f t="shared" si="35"/>
+        <v>-0.24236579877852651</v>
+      </c>
+      <c r="M122" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N122" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B123" t="s">
+        <v>122</v>
+      </c>
+      <c r="C123">
+        <v>11.15</v>
+      </c>
+      <c r="D123">
+        <f>VLOOKUP(B123,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.18</v>
+      </c>
+      <c r="E123">
+        <v>9.82</v>
+      </c>
+      <c r="F123">
+        <f t="shared" si="26"/>
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="G123" t="s">
+        <v>107</v>
+      </c>
+      <c r="I123">
+        <f t="shared" si="32"/>
+        <v>-11.928251121076233</v>
+      </c>
+      <c r="J123">
+        <f t="shared" si="33"/>
+        <v>15.874439461883405</v>
+      </c>
+      <c r="K123">
+        <f t="shared" si="34"/>
+        <v>-11.928251121076233</v>
+      </c>
+      <c r="L123">
+        <f t="shared" si="35"/>
+        <v>-0.75141242937853125</v>
+      </c>
+      <c r="M123" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N123" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B124" t="s">
+        <v>67</v>
+      </c>
+      <c r="C124">
+        <v>58.52</v>
+      </c>
+      <c r="D124">
+        <f>VLOOKUP(B124,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.7</v>
+      </c>
+      <c r="E124">
+        <v>63.075000000000003</v>
+      </c>
+      <c r="F124">
+        <f t="shared" si="26"/>
+        <v>55.970000000000006</v>
+      </c>
+      <c r="G124" t="s">
+        <v>162</v>
+      </c>
+      <c r="I124">
+        <f t="shared" si="32"/>
+        <v>7.7836637047163357</v>
+      </c>
+      <c r="J124">
+        <f t="shared" si="33"/>
+        <v>4.3574846206425102</v>
+      </c>
+      <c r="K124">
+        <f t="shared" si="34"/>
+        <v>7.7836637047163357</v>
+      </c>
+      <c r="L124">
+        <f t="shared" si="35"/>
+        <v>1.7862745098039237</v>
+      </c>
+      <c r="M124" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N124" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B125" t="s">
+        <v>123</v>
+      </c>
+      <c r="C125">
+        <v>10.37</v>
+      </c>
+      <c r="D125">
+        <f>VLOOKUP(B125,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.91759999999999997</v>
+      </c>
+      <c r="E125">
+        <v>11.765000000000001</v>
+      </c>
+      <c r="F125">
+        <f t="shared" si="26"/>
+        <v>8.9935999999999989</v>
+      </c>
+      <c r="G125" t="s">
+        <v>105</v>
+      </c>
+      <c r="I125">
+        <f t="shared" si="32"/>
+        <v>13.452266152362599</v>
+      </c>
+      <c r="J125">
+        <f t="shared" si="33"/>
+        <v>13.272902603664422</v>
+      </c>
+      <c r="K125">
+        <f t="shared" si="34"/>
+        <v>13.452266152362599</v>
+      </c>
+      <c r="L125">
+        <f t="shared" si="35"/>
+        <v>1.0135135135135143</v>
+      </c>
+      <c r="M125" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N125" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B126" t="s">
+        <v>50</v>
+      </c>
+      <c r="C126">
+        <v>4.18</v>
+      </c>
+      <c r="D126">
+        <f>VLOOKUP(B126,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.2452</v>
+      </c>
+      <c r="E126">
+        <v>4.29</v>
+      </c>
+      <c r="F126">
+        <f t="shared" si="26"/>
+        <v>3.8121999999999998</v>
+      </c>
+      <c r="G126" t="s">
+        <v>113</v>
+      </c>
+      <c r="I126">
+        <f t="shared" si="32"/>
+        <v>2.6315789473684288</v>
+      </c>
+      <c r="J126">
+        <f t="shared" si="33"/>
+        <v>8.7990430622009548</v>
+      </c>
+      <c r="K126">
+        <f t="shared" si="34"/>
+        <v>2.6315789473684288</v>
+      </c>
+      <c r="L126">
+        <f t="shared" si="35"/>
+        <v>0.29907558455682531</v>
+      </c>
+      <c r="M126" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N126" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B127" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127">
+        <v>75.67</v>
+      </c>
+      <c r="D127">
+        <f>VLOOKUP(B127,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>1.68</v>
+      </c>
+      <c r="E127">
+        <v>82.37</v>
+      </c>
+      <c r="F127">
+        <f t="shared" si="26"/>
+        <v>73.150000000000006</v>
+      </c>
+      <c r="G127" t="s">
+        <v>294</v>
+      </c>
+      <c r="I127">
+        <f t="shared" si="32"/>
+        <v>8.8542354962336489</v>
+      </c>
+      <c r="J127">
+        <f t="shared" si="33"/>
+        <v>3.3302497687326493</v>
+      </c>
+      <c r="K127">
+        <f t="shared" si="34"/>
+        <v>8.8542354962336489</v>
+      </c>
+      <c r="L127">
+        <f t="shared" si="35"/>
+        <v>2.6587301587301639</v>
+      </c>
+      <c r="M127" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N127" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B128" t="s">
+        <v>246</v>
+      </c>
+      <c r="C128">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="D128">
+        <f>VLOOKUP(B128,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.22</v>
+      </c>
+      <c r="E128">
+        <v>7.86</v>
+      </c>
+      <c r="F128">
+        <f t="shared" si="26"/>
+        <v>7.9599999999999991</v>
+      </c>
+      <c r="G128" t="s">
+        <v>152</v>
+      </c>
+      <c r="I128">
+        <f t="shared" si="32"/>
+        <v>-5.1869722557297813</v>
+      </c>
+      <c r="J128">
+        <f t="shared" si="33"/>
+        <v>3.980699638118216</v>
+      </c>
+      <c r="K128">
+        <f t="shared" si="34"/>
+        <v>-5.1869722557297813</v>
+      </c>
+      <c r="L128">
+        <f t="shared" si="35"/>
+        <v>-1.3030303030302992</v>
+      </c>
+      <c r="M128" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N128" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B129" t="s">
+        <v>123</v>
+      </c>
+      <c r="C129">
+        <v>10.37</v>
+      </c>
+      <c r="D129">
+        <f>VLOOKUP(B129,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.91759999999999997</v>
+      </c>
+      <c r="E129">
+        <v>12.27</v>
+      </c>
+      <c r="F129">
+        <f t="shared" si="26"/>
+        <v>8.9935999999999989</v>
+      </c>
+      <c r="G129" t="s">
+        <v>149</v>
+      </c>
+      <c r="I129">
+        <f t="shared" si="32"/>
+        <v>18.322082931533274</v>
+      </c>
+      <c r="J129">
+        <f t="shared" si="33"/>
+        <v>13.272902603664422</v>
+      </c>
+      <c r="K129">
+        <f t="shared" si="34"/>
+        <v>18.322082931533274</v>
+      </c>
+      <c r="L129">
+        <f t="shared" si="35"/>
+        <v>1.3804126707352511</v>
+      </c>
+      <c r="M129" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N129" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B130" t="s">
+        <v>124</v>
+      </c>
+      <c r="C130">
+        <v>152.18</v>
+      </c>
+      <c r="D130">
+        <f>VLOOKUP(B130,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>2.94</v>
+      </c>
+      <c r="E130">
+        <v>156.24</v>
+      </c>
+      <c r="F130">
+        <f t="shared" si="26"/>
+        <v>147.77000000000001</v>
+      </c>
+      <c r="G130" t="s">
+        <v>233</v>
+      </c>
+      <c r="I130">
+        <f t="shared" si="32"/>
+        <v>2.6678932842686307</v>
+      </c>
+      <c r="J130">
+        <f t="shared" si="33"/>
+        <v>2.8978840846366123</v>
+      </c>
+      <c r="K130">
+        <f t="shared" si="34"/>
+        <v>2.6678932842686307</v>
+      </c>
+      <c r="L130">
+        <f t="shared" si="35"/>
+        <v>0.92063492063492181</v>
+      </c>
+      <c r="M130" t="str">
+        <f t="shared" si="36"/>
+        <v>Win</v>
+      </c>
+      <c r="N130" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B131" t="s">
+        <v>194</v>
+      </c>
+      <c r="C131">
+        <v>13.39</v>
+      </c>
+      <c r="D131">
+        <f>VLOOKUP(B131,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>0.77280000000000004</v>
+      </c>
+      <c r="E131">
+        <v>12.832000000000001</v>
+      </c>
+      <c r="F131">
+        <f t="shared" si="26"/>
+        <v>12.2308</v>
+      </c>
+      <c r="G131" t="s">
+        <v>271</v>
+      </c>
+      <c r="I131">
+        <f t="shared" si="32"/>
+        <v>-4.1672890216579521</v>
+      </c>
+      <c r="J131">
+        <f t="shared" si="33"/>
+        <v>8.6572068707991061</v>
+      </c>
+      <c r="K131">
+        <f t="shared" si="34"/>
+        <v>-4.1672890216579521</v>
+      </c>
+      <c r="L131">
+        <f t="shared" si="35"/>
+        <v>-0.48136645962732888</v>
+      </c>
+      <c r="M131" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N131" t="s">
+        <v>298</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E23:E114">
+  <conditionalFormatting sqref="E23:E131">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$F$2=$A23</formula>
     </cfRule>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E22CE8F-5495-42E5-BDAE-DF1C874C4017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4531476-D89D-46DA-995B-0952D03698B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Results" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="300">
   <si>
     <t>Price</t>
   </si>
@@ -941,7 +940,7 @@
     <t>Stopped out during war volatility</t>
   </si>
   <si>
-    <t>tmdx</t>
+    <t>uuuu</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1444,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>137.27000000000001</v>
+        <v>22.46</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1470,7 +1469,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>127.61000000000001</v>
+        <v>19.355</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1538,7 +1537,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>9.6599999999999966</v>
+        <v>3.1050000000000004</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1563,7 +1562,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>2.0703933747412018</v>
+        <v>6.4412238325281796</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1588,7 +1587,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>36.424564726451514</v>
+        <v>222.61798753339269</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1613,7 +1612,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>2.0703933747412018</v>
+        <v>6.4412238325281796</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1638,7 +1637,7 @@
       </c>
       <c r="H12">
         <f>(H4-H5)*H11</f>
-        <v>20.000000000000004</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
@@ -1663,7 +1662,7 @@
       </c>
       <c r="H13">
         <f>(H12/H2)*100</f>
-        <v>0.25000000000000006</v>
+        <v>0.25</v>
       </c>
       <c r="I13" t="s">
         <v>42</v>
@@ -3521,7 +3520,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2A77BB-0F93-4C87-9B0A-B8954405005E}">
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -3537,7 +3536,7 @@
       </c>
       <c r="B1" s="3">
         <f>COUNTIF(M:M,"Win")/COUNTA(M:M)</f>
-        <v>0.47967479674796748</v>
+        <v>0.46825396825396826</v>
       </c>
       <c r="C1" t="s">
         <v>92</v>
@@ -3558,7 +3557,7 @@
       </c>
       <c r="B3">
         <f>AVERAGEIF(M:M,"Loss",I:I)</f>
-        <v>-4.3508279451477643</v>
+        <v>-4.6969952488484097</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -3567,7 +3566,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.32979683123008535</v>
+        <v>0.2962666251121448</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -3576,7 +3575,7 @@
       </c>
       <c r="B5">
         <f>(B1*B2+(1-B1)*B3)</f>
-        <v>2.1118315800848304</v>
+        <v>1.7738856441829172</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -7440,7 +7439,7 @@
         <v>327.12</v>
       </c>
       <c r="F89">
-        <f t="shared" ref="F89:F131" si="26">C89-(1.5*D89)</f>
+        <f t="shared" ref="F89:F134" si="26">C89-(1.5*D89)</f>
         <v>314.98500000000001</v>
       </c>
       <c r="G89" t="s">
@@ -8791,23 +8790,23 @@
         <v>171</v>
       </c>
       <c r="I117">
-        <f t="shared" ref="I117:I131" si="32">(E117-C117)/C117*(100)</f>
+        <f t="shared" ref="I117:I134" si="32">(E117-C117)/C117*(100)</f>
         <v>1.2972674579078278</v>
       </c>
       <c r="J117">
-        <f t="shared" ref="J117:J131" si="33">(C117-F117)/C117*100</f>
+        <f t="shared" ref="J117:J134" si="33">(C117-F117)/C117*100</f>
         <v>4.3886282086668604</v>
       </c>
       <c r="K117">
-        <f t="shared" ref="K117:K131" si="34">(E117-C117)/C117*100</f>
+        <f t="shared" ref="K117:K134" si="34">(E117-C117)/C117*100</f>
         <v>1.2972674579078278</v>
       </c>
       <c r="L117">
-        <f t="shared" ref="L117:L131" si="35">K117/J117</f>
+        <f t="shared" ref="L117:L134" si="35">K117/J117</f>
         <v>0.29559748427673271</v>
       </c>
       <c r="M117" t="str">
-        <f t="shared" ref="M117:M131" si="36">IF(I117&gt;0,"Win","Loss")</f>
+        <f t="shared" ref="M117:M134" si="36">IF(I117&gt;0,"Win","Loss")</f>
         <v>Win</v>
       </c>
       <c r="N117" t="s">
@@ -9483,6 +9482,141 @@
         <v>Loss</v>
       </c>
       <c r="N131" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B132" t="s">
+        <v>266</v>
+      </c>
+      <c r="C132">
+        <v>177.01</v>
+      </c>
+      <c r="D132">
+        <f>VLOOKUP(B132,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>6.77</v>
+      </c>
+      <c r="E132">
+        <v>166.62</v>
+      </c>
+      <c r="F132">
+        <f t="shared" si="26"/>
+        <v>166.85499999999999</v>
+      </c>
+      <c r="I132">
+        <f t="shared" si="32"/>
+        <v>-5.8697248743008794</v>
+      </c>
+      <c r="J132">
+        <f t="shared" si="33"/>
+        <v>5.7369640133325808</v>
+      </c>
+      <c r="K132">
+        <f t="shared" si="34"/>
+        <v>-5.8697248743008794</v>
+      </c>
+      <c r="L132">
+        <f t="shared" si="35"/>
+        <v>-1.023141309699654</v>
+      </c>
+      <c r="M132" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N132" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B133" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133">
+        <v>22.46</v>
+      </c>
+      <c r="D133">
+        <f>VLOOKUP(B133,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E133">
+        <v>18.824999999999999</v>
+      </c>
+      <c r="F133">
+        <f t="shared" si="26"/>
+        <v>19.355</v>
+      </c>
+      <c r="I133">
+        <f t="shared" si="32"/>
+        <v>-16.184327693677655</v>
+      </c>
+      <c r="J133">
+        <f t="shared" si="33"/>
+        <v>13.824577025823686</v>
+      </c>
+      <c r="K133">
+        <f t="shared" si="34"/>
+        <v>-16.184327693677655</v>
+      </c>
+      <c r="L133">
+        <f t="shared" si="35"/>
+        <v>-1.1706924315619973</v>
+      </c>
+      <c r="M133" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N133" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B134" t="s">
+        <v>293</v>
+      </c>
+      <c r="C134">
+        <v>67.819999999999993</v>
+      </c>
+      <c r="D134">
+        <f>VLOOKUP(B134,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
+        <v>6.21</v>
+      </c>
+      <c r="E134">
+        <v>58.43</v>
+      </c>
+      <c r="F134">
+        <f t="shared" si="26"/>
+        <v>58.504999999999995</v>
+      </c>
+      <c r="I134">
+        <f t="shared" si="32"/>
+        <v>-13.845473311707451</v>
+      </c>
+      <c r="J134">
+        <f t="shared" si="33"/>
+        <v>13.734886464169859</v>
+      </c>
+      <c r="K134">
+        <f t="shared" si="34"/>
+        <v>-13.845473311707451</v>
+      </c>
+      <c r="L134">
+        <f t="shared" si="35"/>
+        <v>-1.0080515297906596</v>
+      </c>
+      <c r="M134" t="str">
+        <f t="shared" si="36"/>
+        <v>Loss</v>
+      </c>
+      <c r="N134" t="s">
         <v>298</v>
       </c>
     </row>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4531476-D89D-46DA-995B-0952D03698B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5125F09B-4BA0-44B9-9020-30AD2C8DCF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="300">
   <si>
     <t>Price</t>
   </si>
@@ -940,7 +940,7 @@
     <t>Stopped out during war volatility</t>
   </si>
   <si>
-    <t>uuuu</t>
+    <t>AVBP</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>22.46</v>
+        <v>24.88</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>19.355</v>
+        <v>22.314999999999998</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>3.1050000000000004</v>
+        <v>2.5650000000000013</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>6.4412238325281796</v>
+        <v>7.797270955165688</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>222.61798753339269</v>
+        <v>200.96463022508038</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>6.4412238325281796</v>
+        <v>7.797270955165688</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -2993,14 +2993,14 @@
         <v>225</v>
       </c>
       <c r="B102">
-        <v>59.2</v>
+        <v>40.85</v>
       </c>
       <c r="C102">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="D102">
         <f t="shared" si="2"/>
-        <v>55.135000000000005</v>
+        <v>35.450000000000003</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -3038,14 +3038,14 @@
         <v>246</v>
       </c>
       <c r="B105">
-        <v>8.08</v>
+        <v>8.16</v>
       </c>
       <c r="C105">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="D105">
         <f>B105-(1.5*C105)</f>
-        <v>7.75</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -3104,7 +3104,7 @@
         <v>2.82</v>
       </c>
       <c r="D109">
-        <f t="shared" ref="D109:D121" si="3">B109-(1.5*C109)</f>
+        <f t="shared" ref="D109:D122" si="3">B109-(1.5*C109)</f>
         <v>87.95</v>
       </c>
     </row>
@@ -3286,6 +3286,21 @@
       <c r="D121">
         <f t="shared" si="3"/>
         <v>58.504999999999995</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>299</v>
+      </c>
+      <c r="B122">
+        <v>24.88</v>
+      </c>
+      <c r="C122">
+        <v>1.71</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="3"/>
+        <v>22.314999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -3566,7 +3581,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.2962666251121448</v>
+        <v>0.29969668462486115</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -7721,14 +7736,14 @@
       </c>
       <c r="D95">
         <f>VLOOKUP(B95,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="E95">
         <v>55.04</v>
       </c>
       <c r="F95">
         <f t="shared" si="26"/>
-        <v>55.135000000000005</v>
+        <v>53.800000000000004</v>
       </c>
       <c r="G95" t="s">
         <v>176</v>
@@ -7739,7 +7754,7 @@
       </c>
       <c r="J95">
         <f t="shared" si="28"/>
-        <v>6.8665540540540499</v>
+        <v>9.1216216216216193</v>
       </c>
       <c r="K95">
         <f t="shared" si="29"/>
@@ -7747,7 +7762,7 @@
       </c>
       <c r="L95">
         <f t="shared" si="30"/>
-        <v>-1.0233702337023385</v>
+        <v>-0.77037037037037126</v>
       </c>
       <c r="M95" t="str">
         <f t="shared" si="31"/>
@@ -7817,14 +7832,14 @@
       </c>
       <c r="D97">
         <f>VLOOKUP(B97,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E97">
         <v>8.73</v>
       </c>
       <c r="F97">
         <f t="shared" si="26"/>
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="G97" t="s">
         <v>113</v>
@@ -7835,7 +7850,7 @@
       </c>
       <c r="J97">
         <f t="shared" si="28"/>
-        <v>4.1405269761606034</v>
+        <v>3.7641154328732727</v>
       </c>
       <c r="K97">
         <f t="shared" si="29"/>
@@ -7843,7 +7858,7 @@
       </c>
       <c r="L97">
         <f t="shared" si="30"/>
-        <v>2.3030303030303045</v>
+        <v>2.5333333333333368</v>
       </c>
       <c r="M97" t="str">
         <f t="shared" si="31"/>
@@ -8057,14 +8072,14 @@
       </c>
       <c r="D102">
         <f>VLOOKUP(B102,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E102">
         <v>8.2200000000000006</v>
       </c>
       <c r="F102">
         <f t="shared" si="26"/>
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="G102" t="s">
         <v>107</v>
@@ -8075,7 +8090,7 @@
       </c>
       <c r="J102">
         <f t="shared" si="28"/>
-        <v>4.1405269761606034</v>
+        <v>3.7641154328732727</v>
       </c>
       <c r="K102">
         <f t="shared" si="29"/>
@@ -8083,7 +8098,7 @@
       </c>
       <c r="L102">
         <f t="shared" si="30"/>
-        <v>0.75757575757576012</v>
+        <v>0.83333333333333681</v>
       </c>
       <c r="M102" t="str">
         <f t="shared" si="31"/>
@@ -9305,14 +9320,14 @@
       </c>
       <c r="D128">
         <f>VLOOKUP(B128,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E128">
         <v>7.86</v>
       </c>
       <c r="F128">
         <f t="shared" si="26"/>
-        <v>7.9599999999999991</v>
+        <v>7.9899999999999993</v>
       </c>
       <c r="G128" t="s">
         <v>152</v>
@@ -9323,7 +9338,7 @@
       </c>
       <c r="J128">
         <f t="shared" si="33"/>
-        <v>3.980699638118216</v>
+        <v>3.6188178528347388</v>
       </c>
       <c r="K128">
         <f t="shared" si="34"/>
@@ -9331,7 +9346,7 @@
       </c>
       <c r="L128">
         <f t="shared" si="35"/>
-        <v>-1.3030303030302992</v>
+        <v>-1.4333333333333302</v>
       </c>
       <c r="M128" t="str">
         <f t="shared" si="36"/>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5125F09B-4BA0-44B9-9020-30AD2C8DCF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866B11CB-A43D-4326-A62D-199E569CA3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="301">
   <si>
     <t>Price</t>
   </si>
@@ -941,6 +941,9 @@
   </si>
   <si>
     <t>AVBP</t>
+  </si>
+  <si>
+    <t>mnst</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1444,7 +1447,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>24.88</v>
+        <v>77.150000000000006</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1469,7 +1472,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>22.314999999999998</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1537,7 +1540,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>2.5650000000000013</v>
+        <v>1.8900000000000006</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>7.797270955165688</v>
+        <v>10.582010582010579</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1587,7 +1590,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>200.96463022508038</v>
+        <v>64.808813998703812</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1612,7 +1615,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>7.797270955165688</v>
+        <v>10.582010582010579</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1748,14 +1751,14 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>79.58</v>
+        <v>77.150000000000006</v>
       </c>
       <c r="C19">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="D19">
-        <f>B19-(0.5*C19)</f>
-        <v>78.739999999999995</v>
+        <f>B19-(1*C19)</f>
+        <v>75.260000000000005</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3581,7 +3584,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.29969668462486115</v>
+        <v>0.29733336892821216</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -9272,14 +9275,14 @@
       </c>
       <c r="D127">
         <f>VLOOKUP(B127,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="E127">
         <v>82.37</v>
       </c>
       <c r="F127">
         <f t="shared" si="26"/>
-        <v>73.150000000000006</v>
+        <v>72.835000000000008</v>
       </c>
       <c r="G127" t="s">
         <v>294</v>
@@ -9290,7 +9293,7 @@
       </c>
       <c r="J127">
         <f t="shared" si="33"/>
-        <v>3.3302497687326493</v>
+        <v>3.7465309898242283</v>
       </c>
       <c r="K127">
         <f t="shared" si="34"/>
@@ -9298,7 +9301,7 @@
       </c>
       <c r="L127">
         <f t="shared" si="35"/>
-        <v>2.6587301587301639</v>
+        <v>2.3633156966490363</v>
       </c>
       <c r="M127" t="str">
         <f t="shared" si="36"/>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866B11CB-A43D-4326-A62D-199E569CA3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D3E123-F9DD-4497-8331-32CC6D4C9A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>75.260000000000005</v>
+        <v>74.300000000000011</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>1.8900000000000006</v>
+        <v>2.8499999999999943</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>10.582010582010579</v>
+        <v>7.0175438596491366</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>10.582010582010579</v>
+        <v>7.0175438596491366</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1754,11 +1754,11 @@
         <v>77.150000000000006</v>
       </c>
       <c r="C19">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="D19">
-        <f>B19-(1*C19)</f>
-        <v>75.260000000000005</v>
+        <f>B19-(1.5*C19)</f>
+        <v>74.300000000000011</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.29733336892821216</v>
+        <v>0.29723386089887954</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -9275,14 +9275,14 @@
       </c>
       <c r="D127">
         <f>VLOOKUP(B127,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="E127">
         <v>82.37</v>
       </c>
       <c r="F127">
         <f t="shared" si="26"/>
-        <v>72.835000000000008</v>
+        <v>72.820000000000007</v>
       </c>
       <c r="G127" t="s">
         <v>294</v>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="J127">
         <f t="shared" si="33"/>
-        <v>3.7465309898242283</v>
+        <v>3.7663539051143045</v>
       </c>
       <c r="K127">
         <f t="shared" si="34"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="L127">
         <f t="shared" si="35"/>
-        <v>2.3633156966490363</v>
+        <v>2.3508771929824617</v>
       </c>
       <c r="M127" t="str">
         <f t="shared" si="36"/>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D3E123-F9DD-4497-8331-32CC6D4C9A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59196FF-A736-4347-9302-B9D1ECC2F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="302">
   <si>
     <t>Price</t>
   </si>
@@ -943,7 +943,10 @@
     <t>AVBP</t>
   </si>
   <si>
-    <t>mnst</t>
+    <t>BDX</t>
+  </si>
+  <si>
+    <t>XLE</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -1392,7 +1395,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1447,7 +1450,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>77.150000000000006</v>
+        <v>58.85</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1472,7 +1475,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>74.300000000000011</v>
+        <v>57.245000000000005</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1540,7 +1543,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>2.8499999999999943</v>
+        <v>1.6049999999999969</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1565,7 +1568,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>7.0175438596491366</v>
+        <v>12.461059190031177</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1590,7 +1593,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>64.808813998703812</v>
+        <v>84.961767204757862</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1615,7 +1618,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>7.0175438596491366</v>
+        <v>12.461059190031177</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1751,14 +1754,14 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>77.150000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="C19">
         <v>1.9</v>
       </c>
       <c r="D19">
         <f>B19-(1.5*C19)</f>
-        <v>74.300000000000011</v>
+        <v>74.350000000000009</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3107,7 +3110,7 @@
         <v>2.82</v>
       </c>
       <c r="D109">
-        <f t="shared" ref="D109:D122" si="3">B109-(1.5*C109)</f>
+        <f t="shared" ref="D109:D124" si="3">B109-(1.5*C109)</f>
         <v>87.95</v>
       </c>
     </row>
@@ -3266,14 +3269,14 @@
         <v>292</v>
       </c>
       <c r="B120">
-        <v>20.69</v>
+        <v>20.81</v>
       </c>
       <c r="C120">
         <v>1.81</v>
       </c>
       <c r="D120">
         <f t="shared" si="3"/>
-        <v>17.975000000000001</v>
+        <v>18.094999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -3304,6 +3307,36 @@
       <c r="D122">
         <f t="shared" si="3"/>
         <v>22.314999999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>300</v>
+      </c>
+      <c r="B123">
+        <v>162.62</v>
+      </c>
+      <c r="C123">
+        <v>4.22</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="3"/>
+        <v>156.29</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>301</v>
+      </c>
+      <c r="B124">
+        <v>58.85</v>
+      </c>
+      <c r="C124">
+        <v>1.07</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="3"/>
+        <v>57.245000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59196FF-A736-4347-9302-B9D1ECC2F67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD659063-646F-4ECE-9AA6-1F83C5C4E492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Loss Calculator" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="304">
   <si>
     <t>Price</t>
   </si>
@@ -947,6 +947,12 @@
   </si>
   <si>
     <t>XLE</t>
+  </si>
+  <si>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>roku</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -1395,7 +1401,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1450,7 +1456,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>58.85</v>
+        <v>92.81</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1475,7 +1481,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>57.245000000000005</v>
+        <v>88.03</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1543,7 +1549,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>1.6049999999999969</v>
+        <v>4.7800000000000011</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1568,7 +1574,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>12.461059190031177</v>
+        <v>4.1841004184100408</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1593,7 +1599,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>84.961767204757862</v>
+        <v>53.873505010235966</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1618,7 +1624,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>12.461059190031177</v>
+        <v>4.1841004184100408</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -2354,14 +2360,14 @@
         <v>116</v>
       </c>
       <c r="B59">
-        <v>92.5</v>
+        <v>92.81</v>
       </c>
       <c r="C59">
         <v>4.78</v>
       </c>
       <c r="D59">
         <f>B59-(1*C59)</f>
-        <v>87.72</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2624,14 +2630,14 @@
         <v>139</v>
       </c>
       <c r="B77">
-        <v>174</v>
+        <v>215.7</v>
       </c>
       <c r="C77">
-        <v>3.46</v>
+        <v>4.47</v>
       </c>
       <c r="D77">
         <f>B77-(1.5*C77)</f>
-        <v>168.81</v>
+        <v>208.99499999999998</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3110,7 +3116,7 @@
         <v>2.82</v>
       </c>
       <c r="D109">
-        <f t="shared" ref="D109:D124" si="3">B109-(1.5*C109)</f>
+        <f t="shared" ref="D109:D125" si="3">B109-(1.5*C109)</f>
         <v>87.95</v>
       </c>
     </row>
@@ -3164,14 +3170,14 @@
         <v>266</v>
       </c>
       <c r="B113">
-        <v>177.01</v>
+        <v>165.12</v>
       </c>
       <c r="C113">
-        <v>6.77</v>
+        <v>6.18</v>
       </c>
       <c r="D113">
         <f t="shared" si="3"/>
-        <v>166.85499999999999</v>
+        <v>155.85</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -3337,6 +3343,21 @@
       <c r="D124">
         <f t="shared" si="3"/>
         <v>57.245000000000005</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>302</v>
+      </c>
+      <c r="B125">
+        <v>166.95</v>
+      </c>
+      <c r="C125">
+        <v>4.8</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="3"/>
+        <v>159.75</v>
       </c>
     </row>
   </sheetData>
@@ -3617,7 +3638,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.29723386089887954</v>
+        <v>0.29539712488142567</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -5423,14 +5444,14 @@
       </c>
       <c r="D46">
         <f>VLOOKUP(B46,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>3.46</v>
+        <v>4.47</v>
       </c>
       <c r="E46">
         <v>177.02</v>
       </c>
       <c r="F46">
         <f t="shared" si="5"/>
-        <v>168.8</v>
+        <v>167.285</v>
       </c>
       <c r="G46" t="s">
         <v>149</v>
@@ -5441,7 +5462,7 @@
       </c>
       <c r="J46">
         <f t="shared" si="12"/>
-        <v>2.9829300534513465</v>
+        <v>3.8536697511351297</v>
       </c>
       <c r="K46">
         <f t="shared" si="13"/>
@@ -5449,7 +5470,7 @@
       </c>
       <c r="L46">
         <f t="shared" si="14"/>
-        <v>0.58381502890173453</v>
+        <v>0.45190156599552506</v>
       </c>
       <c r="M46" t="str">
         <f t="shared" si="15"/>
@@ -9548,14 +9569,14 @@
       </c>
       <c r="D132">
         <f>VLOOKUP(B132,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>6.77</v>
+        <v>6.18</v>
       </c>
       <c r="E132">
         <v>166.62</v>
       </c>
       <c r="F132">
         <f t="shared" si="26"/>
-        <v>166.85499999999999</v>
+        <v>167.73999999999998</v>
       </c>
       <c r="I132">
         <f t="shared" si="32"/>
@@ -9563,7 +9584,7 @@
       </c>
       <c r="J132">
         <f t="shared" si="33"/>
-        <v>5.7369640133325808</v>
+        <v>5.236992260324282</v>
       </c>
       <c r="K132">
         <f t="shared" si="34"/>
@@ -9571,7 +9592,7 @@
       </c>
       <c r="L132">
         <f t="shared" si="35"/>
-        <v>-1.023141309699654</v>
+        <v>-1.1208198489751859</v>
       </c>
       <c r="M132" t="str">
         <f t="shared" si="36"/>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD659063-646F-4ECE-9AA6-1F83C5C4E492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76083AC3-1A37-4312-AE7B-D9FB12148835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
@@ -952,7 +952,7 @@
     <t>NUE</t>
   </si>
   <si>
-    <t>roku</t>
+    <t>pzg</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>92.81</v>
+        <v>1.69</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>88.03</v>
+        <v>1.48</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>4.7800000000000011</v>
+        <v>0.20999999999999996</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>4.1841004184100408</v>
+        <v>95.238095238095255</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>53.873505010235966</v>
+        <v>2958.5798816568049</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>4.1841004184100408</v>
+        <v>95.238095238095255</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1850,14 +1850,14 @@
         <v>52</v>
       </c>
       <c r="B25">
-        <v>120.06</v>
+        <v>138.41999999999999</v>
       </c>
       <c r="C25">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="D25">
         <f>B25-(1*C25)</f>
-        <v>116.73</v>
+        <v>135.01</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2465,14 +2465,14 @@
         <v>126</v>
       </c>
       <c r="B66">
-        <v>15.63</v>
+        <v>13.07</v>
       </c>
       <c r="C66">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="D66">
         <f>B66-(1.5*C66)</f>
-        <v>13.71</v>
+        <v>11.555</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2990,14 +2990,14 @@
         <v>217</v>
       </c>
       <c r="B101">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="C101">
-        <v>8.4599999999999995E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D101">
         <f t="shared" si="2"/>
-        <v>1.3531</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -3320,14 +3320,14 @@
         <v>300</v>
       </c>
       <c r="B123">
-        <v>162.62</v>
+        <v>156.80000000000001</v>
       </c>
       <c r="C123">
-        <v>4.22</v>
+        <v>3.88</v>
       </c>
       <c r="D123">
         <f t="shared" si="3"/>
-        <v>156.29</v>
+        <v>150.98000000000002</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.29539712488142567</v>
+        <v>0.28937074989942763</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="D23">
         <f>VLOOKUP(B23,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="E23">
         <v>127.82</v>
       </c>
       <c r="F23">
         <f t="shared" si="5"/>
-        <v>115.065</v>
+        <v>114.94500000000001</v>
       </c>
       <c r="G23" t="s">
         <v>110</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="J23">
         <f t="shared" si="7"/>
-        <v>4.1604197901049513</v>
+        <v>4.2603698150924494</v>
       </c>
       <c r="K23">
         <f t="shared" si="8"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="L23">
         <f t="shared" si="9"/>
-        <v>1.5535535535535501</v>
+        <v>1.5171065493646134</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="10"/>
@@ -5060,14 +5060,14 @@
       </c>
       <c r="D38">
         <f>VLOOKUP(B38,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="E38">
         <v>14.06</v>
       </c>
       <c r="F38">
         <f t="shared" si="5"/>
-        <v>10.09</v>
+        <v>10.494999999999999</v>
       </c>
       <c r="G38" t="s">
         <v>164</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="J38">
         <f t="shared" si="12"/>
-        <v>15.986677768526228</v>
+        <v>12.614487926727733</v>
       </c>
       <c r="K38">
         <f t="shared" si="13"/>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="L38">
         <f t="shared" si="14"/>
-        <v>1.0677083333333337</v>
+        <v>1.3531353135313529</v>
       </c>
       <c r="M38" t="str">
         <f t="shared" si="15"/>
@@ -5492,14 +5492,14 @@
       </c>
       <c r="D47">
         <f>VLOOKUP(B47,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="E47">
         <v>13.75</v>
       </c>
       <c r="F47">
         <f t="shared" si="5"/>
-        <v>10.07</v>
+        <v>10.475</v>
       </c>
       <c r="G47" t="s">
         <v>155</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="J47">
         <f t="shared" si="12"/>
-        <v>16.013344453711426</v>
+        <v>12.635529608006676</v>
       </c>
       <c r="K47">
         <f t="shared" si="13"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="L47">
         <f t="shared" si="14"/>
-        <v>0.91666666666666652</v>
+        <v>1.1617161716171611</v>
       </c>
       <c r="M47" t="str">
         <f t="shared" si="15"/>
@@ -6833,14 +6833,14 @@
       </c>
       <c r="D75">
         <f>VLOOKUP(B75,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>8.4599999999999995E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E75">
         <v>1.45</v>
       </c>
       <c r="F75">
         <f t="shared" si="5"/>
-        <v>1.3831</v>
+        <v>1.3</v>
       </c>
       <c r="G75" t="s">
         <v>118</v>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="J75">
         <f t="shared" ref="J75:J92" si="22">(C75-F75)/C75*100</f>
-        <v>8.4039735099337758</v>
+        <v>13.90728476821192</v>
       </c>
       <c r="K75">
         <f t="shared" ref="K75:K92" si="23">(E75-C75)/C75*100</f>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="L75">
         <f t="shared" ref="L75:L92" si="24">K75/J75</f>
-        <v>-0.47281323877068593</v>
+        <v>-0.28571428571428598</v>
       </c>
       <c r="M75" t="str">
         <f t="shared" ref="M75:M92" si="25">IF(I75&gt;0,"Win","Loss")</f>
@@ -7169,14 +7169,14 @@
       </c>
       <c r="D82">
         <f>VLOOKUP(B82,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>8.4599999999999995E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E82">
         <v>1.82</v>
       </c>
       <c r="F82">
         <f t="shared" si="5"/>
-        <v>1.3631</v>
+        <v>1.28</v>
       </c>
       <c r="G82" t="s">
         <v>176</v>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="J82">
         <f t="shared" si="22"/>
-        <v>8.5167785234899327</v>
+        <v>14.09395973154362</v>
       </c>
       <c r="K82">
         <f t="shared" si="23"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="L82">
         <f t="shared" si="24"/>
-        <v>2.6004728132387713</v>
+        <v>1.5714285714285721</v>
       </c>
       <c r="M82" t="str">
         <f t="shared" si="25"/>
@@ -7313,14 +7313,14 @@
       </c>
       <c r="D85">
         <f>VLOOKUP(B85,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>8.4599999999999995E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E85">
         <v>1.62</v>
       </c>
       <c r="F85">
         <f t="shared" si="5"/>
-        <v>1.3631</v>
+        <v>1.28</v>
       </c>
       <c r="G85" t="s">
         <v>105</v>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="J85">
         <f t="shared" si="22"/>
-        <v>8.5167785234899327</v>
+        <v>14.09395973154362</v>
       </c>
       <c r="K85">
         <f t="shared" si="23"/>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="L85">
         <f t="shared" si="24"/>
-        <v>1.0244286840031529</v>
+        <v>0.61904761904761973</v>
       </c>
       <c r="M85" t="str">
         <f t="shared" si="25"/>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76083AC3-1A37-4312-AE7B-D9FB12148835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BEE9380-7160-481D-BE52-D42C944987F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
@@ -952,7 +952,7 @@
     <t>NUE</t>
   </si>
   <si>
-    <t>pzg</t>
+    <t>gild</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>1.69</v>
+        <v>140.03</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>1.48</v>
+        <v>136.83000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>0.20999999999999996</v>
+        <v>3.1999999999999886</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>95.238095238095255</v>
+        <v>6.2500000000000222</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>2958.5798816568049</v>
+        <v>35.706634292651572</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>95.238095238095255</v>
+        <v>6.2500000000000222</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1850,14 +1850,14 @@
         <v>52</v>
       </c>
       <c r="B25">
-        <v>138.41999999999999</v>
+        <v>140.03</v>
       </c>
       <c r="C25">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="D25">
         <f>B25-(1*C25)</f>
-        <v>135.01</v>
+        <v>136.83000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.28937074989942763</v>
+        <v>0.29016723083784401</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="D23">
         <f>VLOOKUP(B23,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="E23">
         <v>127.82</v>
       </c>
       <c r="F23">
         <f t="shared" si="5"/>
-        <v>114.94500000000001</v>
+        <v>115.26</v>
       </c>
       <c r="G23" t="s">
         <v>110</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="J23">
         <f t="shared" si="7"/>
-        <v>4.2603698150924494</v>
+        <v>3.9980009995002472</v>
       </c>
       <c r="K23">
         <f t="shared" si="8"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="L23">
         <f t="shared" si="9"/>
-        <v>1.5171065493646134</v>
+        <v>1.6166666666666656</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="10"/>

--- a/entrys and stops.xlsx
+++ b/entrys and stops.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BEE9380-7160-481D-BE52-D42C944987F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71504696-6B68-4B76-A649-311746014AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{700066B9-5A74-44E1-ACE9-D49B5F1E5EBB}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="306">
   <si>
     <t>Price</t>
   </si>
@@ -952,7 +952,13 @@
     <t>NUE</t>
   </si>
   <si>
-    <t>gild</t>
+    <t>SCHD</t>
+  </si>
+  <si>
+    <t>ASAN</t>
+  </si>
+  <si>
+    <t>pltr</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05406170-A489-4C8C-B698-A8974D996514}">
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -1401,7 +1407,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1456,7 +1462,7 @@
       </c>
       <c r="H4">
         <f>VLOOKUP($F$2,$A$3:$D$1000,2,FALSE)</f>
-        <v>140.03</v>
+        <v>144.75</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -1481,7 +1487,7 @@
       </c>
       <c r="H5">
         <f>VLOOKUP($F$2,$A$3:$D$1000,4,FALSE)</f>
-        <v>136.83000000000001</v>
+        <v>138.28</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1505,7 +1511,7 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>5000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1549,7 +1555,7 @@
       </c>
       <c r="H8">
         <f>H4-H5</f>
-        <v>3.1999999999999886</v>
+        <v>6.4699999999999989</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
@@ -1574,7 +1580,7 @@
       </c>
       <c r="H9">
         <f>H7/H8</f>
-        <v>6.2500000000000222</v>
+        <v>3.0911901081916544</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1599,7 +1605,7 @@
       </c>
       <c r="H10">
         <f>H6/H4</f>
-        <v>35.706634292651572</v>
+        <v>0.69084628670120896</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1624,7 +1630,7 @@
       </c>
       <c r="H11">
         <f>MIN(H9,H10)</f>
-        <v>6.2500000000000222</v>
+        <v>0.69084628670120896</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1649,7 +1655,7 @@
       </c>
       <c r="H12">
         <f>(H4-H5)*H11</f>
-        <v>20</v>
+        <v>4.4697754749568208</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
@@ -1674,7 +1680,7 @@
       </c>
       <c r="H13">
         <f>(H12/H2)*100</f>
-        <v>0.25</v>
+        <v>5.587219343696026E-2</v>
       </c>
       <c r="I13" t="s">
         <v>42</v>
@@ -1895,14 +1901,14 @@
         <v>55</v>
       </c>
       <c r="B28">
-        <v>16.260000000000002</v>
+        <v>14.88</v>
       </c>
       <c r="C28">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="D28">
         <f t="shared" si="0"/>
-        <v>14.940000000000001</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2000,14 +2006,14 @@
         <v>63</v>
       </c>
       <c r="B35">
-        <v>11.64</v>
+        <v>10.85</v>
       </c>
       <c r="C35">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="D35">
         <f>B35-(1*C35)</f>
-        <v>10.8</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2210,14 +2216,14 @@
         <v>77</v>
       </c>
       <c r="B49">
-        <v>4.2699999999999996</v>
+        <v>3.02</v>
       </c>
       <c r="C49">
-        <v>0.35</v>
+        <v>0.20849999999999999</v>
       </c>
       <c r="D49">
         <f>B49-(1.5*C49)</f>
-        <v>3.7449999999999997</v>
+        <v>2.7072500000000002</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2255,14 +2261,14 @@
         <v>79</v>
       </c>
       <c r="B52">
-        <v>181.7</v>
+        <v>144.75</v>
       </c>
       <c r="C52">
-        <v>7.4</v>
+        <v>6.47</v>
       </c>
       <c r="D52">
         <f>B52-(1*C52)</f>
-        <v>174.29999999999998</v>
+        <v>138.28</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2630,14 +2636,14 @@
         <v>139</v>
       </c>
       <c r="B77">
-        <v>215.7</v>
+        <v>225.9</v>
       </c>
       <c r="C77">
-        <v>4.47</v>
+        <v>4.84</v>
       </c>
       <c r="D77">
         <f>B77-(1.5*C77)</f>
-        <v>208.99499999999998</v>
+        <v>218.64000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3116,7 +3122,7 @@
         <v>2.82</v>
       </c>
       <c r="D109">
-        <f t="shared" ref="D109:D125" si="3">B109-(1.5*C109)</f>
+        <f t="shared" ref="D109:D127" si="3">B109-(1.5*C109)</f>
         <v>87.95</v>
       </c>
     </row>
@@ -3140,14 +3146,14 @@
         <v>263</v>
       </c>
       <c r="B111">
-        <v>38.32</v>
+        <v>27.18</v>
       </c>
       <c r="C111">
-        <v>4.0199999999999996</v>
+        <v>2.48</v>
       </c>
       <c r="D111">
-        <f t="shared" si="3"/>
-        <v>32.29</v>
+        <f>B111-(1*C111)</f>
+        <v>24.7</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -3155,14 +3161,14 @@
         <v>264</v>
       </c>
       <c r="B112">
-        <v>33.93</v>
+        <v>25.21</v>
       </c>
       <c r="C112">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="D112">
         <f t="shared" si="3"/>
-        <v>30.81</v>
+        <v>22.495000000000001</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -3350,14 +3356,44 @@
         <v>302</v>
       </c>
       <c r="B125">
-        <v>166.95</v>
+        <v>187.81</v>
       </c>
       <c r="C125">
         <v>4.8</v>
       </c>
       <c r="D125">
         <f t="shared" si="3"/>
-        <v>159.75</v>
+        <v>180.61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>303</v>
+      </c>
+      <c r="B126">
+        <v>30.82</v>
+      </c>
+      <c r="C126">
+        <v>0.32</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="3"/>
+        <v>30.34</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>304</v>
+      </c>
+      <c r="B127">
+        <v>7.35</v>
+      </c>
+      <c r="C127">
+        <v>0.45</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="3"/>
+        <v>6.6749999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -3506,15 +3542,15 @@
       </c>
       <c r="B9">
         <f>VLOOKUP(A9,'Stop Loss Calculator'!$A$3:$D$99,2,FALSE)</f>
-        <v>16.260000000000002</v>
+        <v>14.88</v>
       </c>
       <c r="C9">
         <f>VLOOKUP(A9,'Stop Loss Calculator'!$A$3:$D$99,4,FALSE)</f>
-        <v>14.940000000000001</v>
+        <v>13.68</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>37.878787878787868</v>
+        <v>41.666666666666629</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3638,7 +3674,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(L:L)</f>
-        <v>0.29016723083784401</v>
+        <v>0.28993121580502118</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -5444,14 +5480,14 @@
       </c>
       <c r="D46">
         <f>VLOOKUP(B46,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>4.47</v>
+        <v>4.84</v>
       </c>
       <c r="E46">
         <v>177.02</v>
       </c>
       <c r="F46">
         <f t="shared" si="5"/>
-        <v>167.285</v>
+        <v>166.73000000000002</v>
       </c>
       <c r="G46" t="s">
         <v>149</v>
@@ -5462,7 +5498,7 @@
       </c>
       <c r="J46">
         <f t="shared" si="12"/>
-        <v>3.8536697511351297</v>
+        <v>4.1726536007816488</v>
       </c>
       <c r="K46">
         <f t="shared" si="13"/>
@@ -5470,7 +5506,7 @@
       </c>
       <c r="L46">
         <f t="shared" si="14"/>
-        <v>0.45190156599552506</v>
+        <v>0.41735537190082711</v>
       </c>
       <c r="M46" t="str">
         <f t="shared" si="15"/>
@@ -6017,14 +6053,14 @@
       </c>
       <c r="D58">
         <f>VLOOKUP(B58,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>7.4</v>
+        <v>6.47</v>
       </c>
       <c r="E58">
         <v>185.69</v>
       </c>
       <c r="F58">
         <f t="shared" si="5"/>
-        <v>158.22</v>
+        <v>159.61499999999998</v>
       </c>
       <c r="G58" t="s">
         <v>188</v>
@@ -6035,7 +6071,7 @@
       </c>
       <c r="J58">
         <f t="shared" si="12"/>
-        <v>6.5556343019135337</v>
+        <v>5.7317505315379238</v>
       </c>
       <c r="K58">
         <f t="shared" si="13"/>
@@ -6043,7 +6079,7 @@
       </c>
       <c r="L58">
         <f t="shared" si="14"/>
-        <v>1.4747747747747757</v>
+        <v>1.6867594023699106</v>
       </c>
       <c r="M58" t="str">
         <f t="shared" si="15"/>
@@ -8561,14 +8597,14 @@
       </c>
       <c r="D111">
         <f>VLOOKUP(B111,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="E111">
         <v>11.29</v>
       </c>
       <c r="F111">
         <f t="shared" si="26"/>
-        <v>10.38</v>
+        <v>10.665000000000001</v>
       </c>
       <c r="G111" t="s">
         <v>113</v>
@@ -8579,7 +8615,7 @@
       </c>
       <c r="J111">
         <f t="shared" si="28"/>
-        <v>10.824742268041234</v>
+        <v>8.3762886597938113</v>
       </c>
       <c r="K111">
         <f t="shared" si="29"/>
@@ -8587,7 +8623,7 @@
       </c>
       <c r="L111">
         <f t="shared" si="30"/>
-        <v>-0.27777777777777901</v>
+        <v>-0.35897435897436059</v>
       </c>
       <c r="M111" t="str">
         <f t="shared" si="31"/>
@@ -8609,14 +8645,14 @@
       </c>
       <c r="D112">
         <f>VLOOKUP(B112,'Stop Loss Calculator'!$A$3:$D$999,3,FALSE)</f>
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="E112">
         <v>31.3</v>
       </c>
       <c r="F112">
         <f t="shared" si="26"/>
-        <v>30.81</v>
+        <v>31.215</v>
       </c>
       <c r="G112" t="s">
         <v>176</v>
@@ -8627,7 +8663,7 @@
       </c>
       <c r="J112">
         <f t="shared" si="28"/>
-        <v>9.1954022988505777</v>
+        <v>8.0017683465959326</v>
       </c>
       <c r="K112">
         <f t="shared" si="29"/>
@@ -8635,7 +8671,7 @@
       </c>
       <c r="L112">
         <f t="shared" si="30"/>
-        <v>-0.84294871794871729</v>
+        <v>-0.96869244935543242</v>
       </c>
       <c r="M112" t="str">
         <f t="shared" si="31"/>
